--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mercedes\Videos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prg\MC\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40CC96E4-F8D3-45BE-A931-3BE8BD54DBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7839A9-1F57-4F6A-9255-491226502047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="514">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -1534,6 +1534,51 @@
   </si>
   <si>
     <t>F_MENU_AJNAS</t>
+  </si>
+  <si>
+    <t>IsCTRLF9</t>
+  </si>
+  <si>
+    <t>BEDEHKARAN_BESTANKARAN_LIMITED</t>
+  </si>
+  <si>
+    <t>F_MENU_GOZARESH_FROOSH("FK")</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE("CFRALL")</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE("CKRALL")</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE("AMFDAY")</t>
+  </si>
+  <si>
+    <t>❌F_MENU_KHFR("FLIST")</t>
+  </si>
+  <si>
+    <t>F_MENU_FROOSH</t>
+  </si>
+  <si>
+    <t>F_MENU_ANBAR_FRKH("RF")</t>
+  </si>
+  <si>
+    <t>F_MENU_ANBAR_FRKH(RK")</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE("HBGHB")</t>
+  </si>
+  <si>
+    <t>FROOSH_NARAFTAH</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE("CUSTNP")</t>
+  </si>
+  <si>
+    <t>LIST_KHARID</t>
+  </si>
+  <si>
+    <t>LIST_FROOSH</t>
   </si>
 </sst>
 </file>
@@ -1927,7 +1972,7 @@
     <col min="2" max="2" width="52.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="80.42578125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="64.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="48" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2328,7 +2373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2352,7 +2397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2376,7 +2421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2388,7 +2433,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2400,7 +2445,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2422,7 +2467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2446,7 +2491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2473,7 +2518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2500,7 +2545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2527,7 +2572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2545,7 +2590,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2566,7 +2611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2587,7 +2632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2599,7 +2644,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2620,7 +2665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2647,7 +2692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2661,8 +2706,14 @@
       <c r="D32" s="1" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2673,8 +2724,14 @@
       <c r="C33" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2695,7 +2752,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2722,7 +2779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2749,7 +2806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3712,7 +3769,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -3736,7 +3793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -3760,7 +3817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -3784,7 +3841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -3808,7 +3865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -3835,7 +3892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -3862,7 +3919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -3889,7 +3946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -3913,7 +3970,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -3924,8 +3981,11 @@
       <c r="C101" s="5" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D101" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -3952,7 +4012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -3963,8 +4023,11 @@
       <c r="C103" s="5" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D103" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -3975,8 +4038,11 @@
       <c r="C104" s="5" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D104" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -3987,8 +4053,11 @@
       <c r="C105" s="5" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D105" s="1" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -3999,8 +4068,11 @@
       <c r="C106" s="5" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D106" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4011,8 +4083,11 @@
       <c r="C107" s="5" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D107" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -4023,8 +4098,11 @@
       <c r="C108" s="5" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D108" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -4035,8 +4113,11 @@
       <c r="C109" s="5" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D109" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4047,8 +4128,11 @@
       <c r="C110" s="5" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D110" s="1" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4059,8 +4143,11 @@
       <c r="C111" s="5" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D111" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4071,8 +4158,11 @@
       <c r="C112" s="5" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D112" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4083,8 +4173,11 @@
       <c r="C113" s="5" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D113" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4095,8 +4188,11 @@
       <c r="C114" s="5" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D114" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4107,8 +4203,11 @@
       <c r="C115" s="5" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D115" s="1" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -4119,8 +4218,11 @@
       <c r="C116" s="5" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D116" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -4131,8 +4233,11 @@
       <c r="C117" s="5" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D117" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4143,8 +4248,11 @@
       <c r="C118" s="5" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D118" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -4155,8 +4263,11 @@
       <c r="C119" s="5" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D119" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -4167,8 +4278,11 @@
       <c r="C120" s="5" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D120" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -4178,6 +4292,9 @@
       </c>
       <c r="C121" s="5" t="s">
         <v>191</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
@@ -4240,7 +4357,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -4255,7 +4372,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -4273,7 +4390,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -4291,7 +4408,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -4306,7 +4423,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -4324,7 +4441,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -4336,7 +4453,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <f t="shared" ref="A133:A196" si="2">A132+1</f>
         <v>132</v>
@@ -4351,7 +4468,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -4363,7 +4480,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -4375,7 +4492,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -4387,7 +4504,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -4399,7 +4516,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -4411,7 +4528,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -4423,7 +4540,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -4435,7 +4552,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -4447,7 +4564,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -5392,7 +5509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -5404,7 +5521,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -5416,7 +5533,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -5440,7 +5557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -5452,7 +5569,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -5464,7 +5581,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -5476,7 +5593,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -5488,7 +5605,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -5500,7 +5617,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -5512,7 +5629,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <f t="shared" ref="A197:A260" si="3">A196+1</f>
         <v>196</v>
@@ -5524,7 +5641,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <f t="shared" si="3"/>
         <v>197</v>
@@ -5536,7 +5653,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <f t="shared" si="3"/>
         <v>198</v>
@@ -5548,7 +5665,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -5560,7 +5677,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -5572,7 +5689,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -5584,7 +5701,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -6927,7 +7044,13 @@
   <autoFilter ref="A1:K294" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="خرید فروش - عملیات ویزیتوری"/>
+        <filter val="چکها - سایر گزارشات"/>
+        <filter val="چکها - سایر گزارشات - چاپ برگه به حساب گذاشتن چک"/>
+        <filter val="چکها - سایر گزارشات - چاپ چکهای پرداختی"/>
+        <filter val="خرید فروش - گزارشات خرید فروش"/>
+        <filter val="خرید فروش - گزارشات خرید فروش - سایر"/>
+        <filter val="خرید فروش - گزارشات خرید فروش - گزارشات دارایی"/>
+        <filter val="گزارشات حسابداری"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\prg\MC\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\prg\MrCorrect\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7839A9-1F57-4F6A-9255-491226502047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$294</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="517">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -1579,17 +1578,26 @@
   </si>
   <si>
     <t>LIST_FROOSH</t>
+  </si>
+  <si>
+    <t>WIN_TOZIE</t>
+  </si>
+  <si>
+    <t>VISITOR_DAY_HEAD</t>
+  </si>
+  <si>
+    <t>WIN_VISIT_ROUTE_FORM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
@@ -1963,26 +1971,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K294"/>
-  <sheetFormatPr defaultColWidth="21.5703125" defaultRowHeight="22.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="22.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="80.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="48" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="21.5703125" style="1"/>
+    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="21.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>63</v>
       </c>
@@ -2017,7 +2024,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2043,7 +2050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -2070,7 +2077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -2097,7 +2104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2121,7 +2128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2145,7 +2152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2169,7 +2176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2193,7 +2200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2217,7 +2224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2241,7 +2248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2265,7 +2272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2286,7 +2293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2310,7 +2317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2325,7 +2332,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2349,7 +2356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2373,7 +2380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2397,7 +2404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2421,7 +2428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2433,7 +2440,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2445,7 +2452,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2467,7 +2474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2491,7 +2498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2518,7 +2525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2545,7 +2552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2572,7 +2579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2590,7 +2597,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2611,7 +2618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2632,7 +2639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2644,7 +2651,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2665,7 +2672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2692,7 +2699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2713,7 +2720,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2731,7 +2738,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2752,7 +2759,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2779,7 +2786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2806,7 +2813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2833,7 +2840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2857,7 +2864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2881,7 +2888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2893,7 +2900,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2917,7 +2924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2941,7 +2948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -2959,7 +2966,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -2983,7 +2990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3004,7 +3011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3025,7 +3032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3046,7 +3053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3067,7 +3074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3079,7 +3086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3091,7 +3098,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3103,7 +3110,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3130,7 +3137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3151,7 +3158,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3178,7 +3185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3205,7 +3212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3232,7 +3239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3244,7 +3251,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3256,7 +3263,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3268,7 +3275,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3280,7 +3287,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3292,7 +3299,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3304,7 +3311,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3316,7 +3323,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3328,7 +3335,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3355,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3382,7 +3389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -3394,7 +3401,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <f t="shared" ref="A68:A132" si="1">A67+1</f>
         <v>67</v>
@@ -3406,7 +3413,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -3418,7 +3425,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -3430,7 +3437,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -3442,7 +3449,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -3454,7 +3461,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -3466,7 +3473,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -3478,7 +3485,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -3490,7 +3497,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -3502,7 +3509,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -3514,7 +3521,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -3526,7 +3533,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -3538,7 +3545,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -3550,7 +3557,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -3562,7 +3569,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -3574,7 +3581,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -3598,7 +3605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -3616,7 +3623,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -3640,7 +3647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -3652,7 +3659,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -3667,7 +3674,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -3691,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -3715,7 +3722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -3739,7 +3746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -3754,7 +3761,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -3769,7 +3776,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -3793,7 +3800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -3817,7 +3824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -3841,7 +3848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -3865,7 +3872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -3892,7 +3899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -3919,7 +3926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -3946,7 +3953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -3970,7 +3977,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -3985,7 +3992,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4012,7 +4019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -4027,7 +4034,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4042,7 +4049,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4057,7 +4064,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4072,7 +4079,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4087,7 +4094,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -4102,7 +4109,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -4117,7 +4124,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4132,7 +4139,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4147,7 +4154,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4162,7 +4169,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4177,7 +4184,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4192,7 +4199,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4207,7 +4214,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -4222,7 +4229,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -4237,7 +4244,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4252,7 +4259,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -4267,7 +4274,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -4282,7 +4289,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -4297,7 +4304,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -4309,7 +4316,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -4321,7 +4328,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -4333,7 +4340,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -4345,7 +4352,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -4357,7 +4364,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -4372,7 +4379,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -4390,7 +4397,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -4408,7 +4415,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -4423,7 +4430,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -4441,7 +4448,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -4452,8 +4459,23 @@
       <c r="C132" s="5" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D132" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G132" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H132" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I132" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <f t="shared" ref="A133:A196" si="2">A132+1</f>
         <v>132</v>
@@ -4468,7 +4490,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -4479,8 +4501,23 @@
       <c r="C134" s="5" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D134" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G134" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H134" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I134" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -4491,8 +4528,23 @@
       <c r="C135" s="5" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D135" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="G135" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H135" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I135" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -4504,7 +4556,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -4516,7 +4568,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -4528,7 +4580,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -4540,7 +4592,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -4552,7 +4604,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -4564,7 +4616,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -4576,7 +4628,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -4588,7 +4640,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -4600,7 +4652,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -4624,7 +4676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -4648,7 +4700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -4672,7 +4724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -4690,7 +4742,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -4714,7 +4766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -4738,7 +4790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -4762,7 +4814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -4780,7 +4832,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -4804,7 +4856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -4831,7 +4883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -4855,7 +4907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -4876,7 +4928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -4900,7 +4952,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -4924,7 +4976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -4948,7 +5000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -4972,7 +5024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -4999,7 +5051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5023,7 +5075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -5047,7 +5099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -5071,7 +5123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -5095,7 +5147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5119,7 +5171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -5143,7 +5195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -5158,7 +5210,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -5170,7 +5222,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -5182,7 +5234,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -5194,7 +5246,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -5215,7 +5267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -5236,7 +5288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -5260,7 +5312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -5281,7 +5333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -5302,7 +5354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -5323,7 +5375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -5344,7 +5396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -5359,7 +5411,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -5380,7 +5432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -5401,7 +5453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -5413,7 +5465,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -5425,7 +5477,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -5446,7 +5498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -5461,7 +5513,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -5488,7 +5540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -5509,7 +5561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -5521,7 +5573,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -5533,7 +5585,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -5557,7 +5609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -5569,7 +5621,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -5581,7 +5633,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -5593,7 +5645,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -5605,7 +5657,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -5617,7 +5669,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -5629,7 +5681,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <f t="shared" ref="A197:A260" si="3">A196+1</f>
         <v>196</v>
@@ -5641,7 +5693,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <f t="shared" si="3"/>
         <v>197</v>
@@ -5653,7 +5705,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <f t="shared" si="3"/>
         <v>198</v>
@@ -5665,7 +5717,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -5677,7 +5729,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -5689,7 +5741,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -5701,7 +5753,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -5713,7 +5765,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -5725,7 +5777,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -5737,7 +5789,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -5758,7 +5810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -5770,7 +5822,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -5782,7 +5834,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -5794,7 +5846,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -5806,7 +5858,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -5818,7 +5870,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -5830,7 +5882,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -5842,7 +5894,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -5854,7 +5906,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -5866,7 +5918,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -5878,7 +5930,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -5890,7 +5942,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -5902,7 +5954,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -5914,7 +5966,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -5926,7 +5978,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -5938,7 +5990,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -5950,7 +6002,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -5962,7 +6014,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -5974,7 +6026,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -5986,7 +6038,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -5998,7 +6050,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6010,7 +6062,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6022,7 +6074,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6034,7 +6086,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -6046,7 +6098,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6058,7 +6110,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -6070,7 +6122,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -6082,7 +6134,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -6094,7 +6146,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -6106,7 +6158,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -6118,7 +6170,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -6130,7 +6182,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -6142,7 +6194,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6154,7 +6206,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -6166,7 +6218,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -6178,7 +6230,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -6190,7 +6242,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6202,7 +6254,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6214,7 +6266,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6226,7 +6278,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6238,7 +6290,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6262,7 +6314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6286,7 +6338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -6298,7 +6350,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -6310,7 +6362,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -6322,7 +6374,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -6334,7 +6386,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -6346,7 +6398,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -6370,7 +6422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -6382,7 +6434,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -6394,7 +6446,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -6406,7 +6458,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -6418,7 +6470,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -6430,7 +6482,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -6442,7 +6494,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <f t="shared" ref="A261:A292" si="4">A260+1</f>
         <v>260</v>
@@ -6454,7 +6506,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <f t="shared" si="4"/>
         <v>261</v>
@@ -6466,7 +6518,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <f t="shared" si="4"/>
         <v>262</v>
@@ -6478,7 +6530,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <f t="shared" si="4"/>
         <v>263</v>
@@ -6490,7 +6542,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -6514,7 +6566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -6538,7 +6590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -6550,7 +6602,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -6574,7 +6626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -6598,7 +6650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -6610,7 +6662,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -6622,7 +6674,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -6634,7 +6686,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <f t="shared" si="4"/>
         <v>272</v>
@@ -6646,7 +6698,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <f t="shared" si="4"/>
         <v>273</v>
@@ -6658,7 +6710,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <f t="shared" si="4"/>
         <v>274</v>
@@ -6670,7 +6722,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -6682,7 +6734,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -6694,7 +6746,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -6706,7 +6758,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <f t="shared" si="4"/>
         <v>278</v>
@@ -6718,7 +6770,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -6730,7 +6782,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -6757,7 +6809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <f t="shared" si="4"/>
         <v>281</v>
@@ -6781,7 +6833,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <f t="shared" si="4"/>
         <v>282</v>
@@ -6805,7 +6857,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -6826,7 +6878,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <f t="shared" si="4"/>
         <v>284</v>
@@ -6850,7 +6902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <f t="shared" si="4"/>
         <v>285</v>
@@ -6871,7 +6923,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <f t="shared" si="4"/>
         <v>286</v>
@@ -6898,7 +6950,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -6925,7 +6977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <f t="shared" si="4"/>
         <v>288</v>
@@ -6946,7 +6998,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -6970,7 +7022,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <f t="shared" si="4"/>
         <v>290</v>
@@ -6991,7 +7043,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <f t="shared" si="4"/>
         <v>291</v>
@@ -7015,7 +7067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B293" s="1" t="s">
         <v>19</v>
       </c>
@@ -7035,25 +7087,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C294" s="5" t="s">
         <v>428</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K294" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="چکها - سایر گزارشات"/>
-        <filter val="چکها - سایر گزارشات - چاپ برگه به حساب گذاشتن چک"/>
-        <filter val="چکها - سایر گزارشات - چاپ چکهای پرداختی"/>
-        <filter val="خرید فروش - گزارشات خرید فروش"/>
-        <filter val="خرید فروش - گزارشات خرید فروش - سایر"/>
-        <filter val="خرید فروش - گزارشات خرید فروش - گزارشات دارایی"/>
-        <filter val="گزارشات حسابداری"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K294"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -1972,6 +1972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K294"/>
   <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="22.5" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2024,7 +2025,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2050,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -2077,7 +2078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -2474,7 +2475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2498,7 +2499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2525,7 +2526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2552,7 +2553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2618,7 +2619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2651,7 +2652,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2672,7 +2673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2759,7 +2760,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2786,7 +2787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2813,7 +2814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2924,7 +2925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3011,7 +3012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3032,7 +3033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3053,7 +3054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3110,7 +3111,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3158,7 +3159,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3185,7 +3186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3212,7 +3213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3335,7 +3336,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3362,7 +3363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3872,7 +3873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -3899,7 +3900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -3926,7 +3927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -3992,7 +3993,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4448,7 +4449,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -4490,7 +4491,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -4517,7 +4518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -4856,7 +4857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5051,7 +5052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5288,7 +5289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -5354,7 +5355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -5411,7 +5412,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -5513,7 +5514,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -5540,7 +5541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -5585,7 +5586,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -5789,7 +5790,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6290,7 +6291,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6314,7 +6315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6950,7 +6951,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -7043,7 +7044,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <f t="shared" si="4"/>
         <v>291</v>
@@ -7093,7 +7094,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K294"/>
+  <autoFilter ref="A1:K294">
+    <filterColumn colId="6">
+      <filters blank="1">
+        <filter val="???"/>
+        <filter val="FALSE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="549">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -191,9 +191,6 @@
     <t>گزارش تراز آزمایشی چهار ستونی حسابهای کل</t>
   </si>
   <si>
-    <t>گزارش تراز آزمایشی حسابهای کل , معین , تفضیلی</t>
-  </si>
-  <si>
     <t>گزارش تراز آزمایشی چهار ستونی حسابهای تفضیلی</t>
   </si>
   <si>
@@ -1587,6 +1584,105 @@
   </si>
   <si>
     <t>WIN_VISIT_ROUTE_FORM</t>
+  </si>
+  <si>
+    <t>TCOD_MARKAZHAZ_WIN</t>
+  </si>
+  <si>
+    <t>TAKHFIF_DEF_FORM</t>
+  </si>
+  <si>
+    <t>FMENU_TARAZ_4_RT4</t>
+  </si>
+  <si>
+    <t>گزارش تراز آزمایشی چهار ستونی حسابهای کل ، معین و تفضیلی</t>
+  </si>
+  <si>
+    <t>FMENU_TARAZ_4_RFT4T</t>
+  </si>
+  <si>
+    <t>TARAZHES_WIN</t>
+  </si>
+  <si>
+    <t>WIN_HEAD_MANF_FORMULSAKHT</t>
+  </si>
+  <si>
+    <t>WIN_HEAD_MANF</t>
+  </si>
+  <si>
+    <t>HAVALE_EXIT_SAYER</t>
+  </si>
+  <si>
+    <t>AMAR_TOLID</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE_AMMAS</t>
+  </si>
+  <si>
+    <t>AMAR_FROOSH_KOL</t>
+  </si>
+  <si>
+    <t>AMAR_FROOSH_KOL_ALL</t>
+  </si>
+  <si>
+    <t>F_MENU_GOZARESH_FROOSH_FK</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE_CFRALL</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE_CKRALL</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE_AMFDAY</t>
+  </si>
+  <si>
+    <t>WIN_F_MENU_KHFR_FLIST</t>
+  </si>
+  <si>
+    <t>WIN_F_MENU_KHFR_KLIST</t>
+  </si>
+  <si>
+    <t>F_MENU_ANBAR_FRKH_RK</t>
+  </si>
+  <si>
+    <t>HEAD_SERCH_MAIN_F12</t>
+  </si>
+  <si>
+    <t>HEAD_SERCH_MAIN_ADVANC_F12</t>
+  </si>
+  <si>
+    <t>F_MENU_KOL_MOIN_TAFZIL_VAZ</t>
+  </si>
+  <si>
+    <t>F_MENU_KOL_MOIN_TAFZIL_FRKMA4</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE_HBGHB</t>
+  </si>
+  <si>
+    <t>WIN_F_MENU_KHFR_FONARP</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE_CUSTNP</t>
+  </si>
+  <si>
+    <t>F_MENU_GOZARESH_FROOSH_F</t>
+  </si>
+  <si>
+    <t>F_MENU_GOZARESH_FROOSH_FR</t>
+  </si>
+  <si>
+    <t>RAAS</t>
+  </si>
+  <si>
+    <t>STUF_DEF_LIST</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE_VISIT_VISITKALMA</t>
+  </si>
+  <si>
+    <t>F_MENU_DATE_VISIT_VISITONE</t>
   </si>
 </sst>
 </file>
@@ -1972,19 +2068,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K294"/>
   <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="22.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="80.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.25" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.75" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="21.625" style="1"/>
@@ -1992,7 +2087,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -2001,31 +2096,31 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2036,10 +2131,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -2051,7 +2146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -2063,10 +2158,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -2078,7 +2173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -2087,13 +2182,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>1</v>
@@ -2117,10 +2212,13 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
+      </c>
+      <c r="G5" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H5" s="1" t="b">
         <v>1</v>
@@ -2138,13 +2236,16 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
+      </c>
+      <c r="G6" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H6" s="1" t="b">
         <v>1</v>
@@ -2165,10 +2266,13 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
+      </c>
+      <c r="G7" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="b">
         <v>1</v>
@@ -2189,10 +2293,13 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
+      </c>
+      <c r="G8" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="b">
         <v>1</v>
@@ -2213,10 +2320,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
+      </c>
+      <c r="G9" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="b">
         <v>1</v>
@@ -2237,10 +2347,13 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
+      </c>
+      <c r="G10" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="b">
         <v>1</v>
@@ -2261,10 +2374,13 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
+      </c>
+      <c r="G11" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H11" s="1" t="b">
         <v>1</v>
@@ -2279,18 +2395,24 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>121</v>
-      </c>
       <c r="D12" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
+      </c>
+      <c r="G12" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2306,10 +2428,13 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
+      </c>
+      <c r="G13" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H13" s="1" t="b">
         <v>1</v>
@@ -2327,10 +2452,19 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>472</v>
+      <c r="G14" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -2345,10 +2479,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
+      </c>
+      <c r="G15" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H15" s="1" t="b">
         <v>1</v>
@@ -2369,10 +2506,13 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
+      </c>
+      <c r="G16" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="b">
         <v>1</v>
@@ -2393,10 +2533,13 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
+      </c>
+      <c r="G17" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="b">
         <v>1</v>
@@ -2417,10 +2560,13 @@
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
+      </c>
+      <c r="G18" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H18" s="1" t="b">
         <v>1</v>
@@ -2440,6 +2586,21 @@
       <c r="C19" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="D19" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
@@ -2452,6 +2613,18 @@
       <c r="C20" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="G20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -2465,17 +2638,23 @@
         <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F21" s="3"/>
+      <c r="G21" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="I21" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2487,10 +2666,10 @@
         <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G22" s="1" t="b">
         <v>1</v>
@@ -2499,7 +2678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2511,10 +2690,10 @@
         <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G23" s="1" t="b">
         <v>1</v>
@@ -2526,7 +2705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2538,10 +2717,10 @@
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -2553,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2565,10 +2744,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -2592,10 +2771,16 @@
         <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>345</v>
+        <v>410</v>
+      </c>
+      <c r="G26" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -2610,16 +2795,22 @@
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>411</v>
+        <v>344</v>
+      </c>
+      <c r="G27" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H27" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I27" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2631,10 +2822,10 @@
         <v>28</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G28" s="1" t="b">
         <v>1</v>
@@ -2652,7 +2843,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2664,7 +2855,7 @@
         <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G30" s="1" t="b">
         <v>1</v>
@@ -2673,7 +2864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2685,10 +2876,10 @@
         <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -2712,13 +2903,22 @@
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
+      </c>
+      <c r="G32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -2733,10 +2933,19 @@
         <v>33</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
+      </c>
+      <c r="G33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
@@ -2751,16 +2960,16 @@
         <v>34</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2772,11 +2981,11 @@
         <v>35</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="G35" s="1" t="b">
         <v>1</v>
       </c>
@@ -2787,7 +2996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2799,10 +3008,10 @@
         <v>36</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -2814,7 +3023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2826,10 +3035,10 @@
         <v>37</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G37" s="1" t="b">
         <v>1</v>
@@ -2853,10 +3062,13 @@
         <v>38</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
+      </c>
+      <c r="G38" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H38" s="1" t="b">
         <v>1</v>
@@ -2877,10 +3089,13 @@
         <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
+      </c>
+      <c r="G39" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H39" s="1" t="b">
         <v>1</v>
@@ -2913,10 +3128,13 @@
         <v>41</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
+      </c>
+      <c r="G41" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H41" s="1" t="b">
         <v>1</v>
@@ -2925,7 +3143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2934,13 +3152,13 @@
         <v>19</v>
       </c>
       <c r="C42" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G42" s="1" t="b">
         <v>1</v>
@@ -2961,10 +3179,16 @@
         <v>42</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
+      </c>
+      <c r="G43" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
@@ -2979,10 +3203,13 @@
         <v>44</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
+      </c>
+      <c r="G44" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H44" s="1" t="b">
         <v>1</v>
@@ -3003,16 +3230,22 @@
         <v>45</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
+      </c>
+      <c r="G45" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H45" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="I45" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3024,16 +3257,16 @@
         <v>47</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G46" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3045,16 +3278,16 @@
         <v>48</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G47" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3066,10 +3299,10 @@
         <v>49</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -3086,6 +3319,21 @@
       <c r="C49" s="5" t="s">
         <v>50</v>
       </c>
+      <c r="D49" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="G49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
@@ -3096,7 +3344,19 @@
         <v>46</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>51</v>
+        <v>519</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
@@ -3108,10 +3368,10 @@
         <v>46</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3120,13 +3380,13 @@
         <v>46</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -3147,19 +3407,25 @@
         <v>46</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+      <c r="G53" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I53" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3168,14 +3434,14 @@
         <v>46</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="G54" s="1" t="b">
         <v>1</v>
       </c>
@@ -3186,7 +3452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3195,13 +3461,13 @@
         <v>46</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G55" s="1" t="b">
         <v>1</v>
@@ -3213,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3222,13 +3488,13 @@
         <v>46</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -3249,7 +3515,19 @@
         <v>46</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="G57" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H57" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I57" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
@@ -3258,10 +3536,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
@@ -3270,10 +3548,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
@@ -3282,10 +3560,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
@@ -3294,10 +3572,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
@@ -3309,7 +3587,7 @@
         <v>19</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
@@ -3321,7 +3599,7 @@
         <v>19</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
@@ -3330,28 +3608,43 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+      <c r="D64" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="G64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G65" s="1" t="b">
         <v>1</v>
@@ -3363,22 +3656,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G66" s="1" t="b">
         <v>1</v>
@@ -3396,10 +3689,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="G67" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
@@ -3408,10 +3713,10 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
@@ -3420,10 +3725,10 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
@@ -3432,10 +3737,25 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="G70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I70" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
@@ -3444,10 +3764,22 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="G71" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H71" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
@@ -3456,10 +3788,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
@@ -3468,10 +3800,10 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
@@ -3480,10 +3812,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -3492,10 +3824,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -3504,10 +3836,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -3516,10 +3848,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -3528,10 +3860,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -3540,10 +3872,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -3552,10 +3884,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
@@ -3564,10 +3896,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G81" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H81" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
@@ -3576,10 +3920,22 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G82" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H82" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
@@ -3588,16 +3944,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
+      </c>
+      <c r="G83" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H83" s="1" t="b">
         <v>1</v>
@@ -3612,16 +3971,25 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="D84" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
+      </c>
+      <c r="G84" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H84" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
@@ -3630,16 +3998,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
+      </c>
+      <c r="G85" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H85" s="1" t="b">
         <v>1</v>
@@ -3654,10 +4025,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
@@ -3666,13 +4037,22 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
@@ -3681,16 +4061,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C88" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H88" s="1" t="b">
         <v>1</v>
@@ -3705,16 +4085,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
+      </c>
+      <c r="G89" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H89" s="1" t="b">
         <v>1</v>
@@ -3729,16 +4112,19 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C90" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
+      </c>
+      <c r="G90" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H90" s="1" t="b">
         <v>1</v>
@@ -3753,13 +4139,19 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G91" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
@@ -3768,13 +4160,19 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G92" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
@@ -3783,16 +4181,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H93" s="1" t="b">
         <v>1</v>
@@ -3807,16 +4205,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C94" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>384</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>385</v>
       </c>
       <c r="H94" s="1" t="b">
         <v>1</v>
@@ -3831,16 +4229,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>163</v>
-      </c>
       <c r="D95" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H95" s="1" t="b">
         <v>1</v>
@@ -3855,16 +4253,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H96" s="1" t="b">
         <v>1</v>
@@ -3873,22 +4271,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G97" s="1" t="b">
         <v>1</v>
@@ -3900,22 +4298,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G98" s="1" t="b">
         <v>1</v>
@@ -3927,22 +4325,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G99" s="1" t="b">
         <v>1</v>
@@ -3960,22 +4358,22 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C100" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C100" s="5" t="s">
-        <v>169</v>
-      </c>
       <c r="D100" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H100" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
@@ -3984,31 +4382,43 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="G101" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I101" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G102" s="1" t="b">
         <v>1</v>
@@ -4026,13 +4436,22 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="G103" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
@@ -4041,13 +4460,22 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="G104" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H104" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
@@ -4056,13 +4484,22 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="G105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
@@ -4071,13 +4508,22 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="G106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
@@ -4086,13 +4532,22 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G107" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I107" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
@@ -4101,13 +4556,25 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G108" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H108" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
@@ -4116,13 +4583,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
+      </c>
+      <c r="F109" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
@@ -4131,13 +4601,25 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="G110" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H110" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I110" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
@@ -4146,13 +4628,25 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>436</v>
+        <v>536</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="G111" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H111" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I111" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
@@ -4161,13 +4655,25 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>436</v>
+        <v>537</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="G112" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H112" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.2">
@@ -4176,13 +4682,25 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>436</v>
+        <v>181</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="G113" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H113" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I113" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
@@ -4191,13 +4709,25 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>436</v>
+        <v>539</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="G114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H114" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I114" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
@@ -4206,13 +4736,25 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="G115" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H115" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I115" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
@@ -4221,13 +4763,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
@@ -4236,13 +4778,19 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="G117" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
@@ -4251,13 +4799,19 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C118" s="5" t="s">
-        <v>188</v>
-      </c>
       <c r="D118" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G118" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -4266,13 +4820,19 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="G119" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.2">
@@ -4281,13 +4841,19 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="G120" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.2">
@@ -4296,13 +4862,19 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="G121" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.2">
@@ -4311,10 +4883,25 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="G122" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H122" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I122" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
@@ -4323,10 +4910,19 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C123" s="5" t="s">
-        <v>194</v>
+      <c r="D123" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G123" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
@@ -4335,10 +4931,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
@@ -4347,10 +4943,25 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G125" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H125" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I125" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
@@ -4359,10 +4970,19 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="G126" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
@@ -4371,13 +4991,16 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
+      </c>
+      <c r="F127" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.2">
@@ -4386,16 +5009,19 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>200</v>
-      </c>
       <c r="D128" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F128" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J128" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
@@ -4404,16 +5030,22 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="G129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J129" s="1" t="s">
         <v>493</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
@@ -4422,13 +5054,22 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="G130" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H130" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
@@ -4437,34 +5078,43 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="G131" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H131" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" si="1"/>
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G132" s="1" t="b">
         <v>1</v>
@@ -4482,31 +5132,31 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G134" s="1" t="b">
         <v>1</v>
@@ -4518,22 +5168,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G135" s="1" t="b">
         <v>1</v>
@@ -4551,10 +5201,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
@@ -4563,10 +5213,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
@@ -4575,10 +5225,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -4587,10 +5237,10 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
@@ -4599,10 +5249,10 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
@@ -4611,10 +5261,10 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
@@ -4623,10 +5273,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
@@ -4635,10 +5285,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
@@ -4647,10 +5297,10 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
@@ -4659,16 +5309,16 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H145" s="1" t="b">
         <v>1</v>
@@ -4683,16 +5333,16 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C146" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C146" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="D146" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H146" s="1" t="b">
         <v>1</v>
@@ -4707,16 +5357,16 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H147" s="1" t="b">
         <v>1</v>
@@ -4731,16 +5381,16 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
@@ -4749,16 +5399,16 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H149" s="1" t="b">
         <v>1</v>
@@ -4773,16 +5423,16 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H150" s="1" t="b">
         <v>1</v>
@@ -4797,16 +5447,16 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H151" s="1" t="b">
         <v>1</v>
@@ -4821,16 +5471,16 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
@@ -4839,16 +5489,16 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H153" s="1" t="b">
         <v>1</v>
@@ -4857,22 +5507,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G154" s="1" t="b">
         <v>1</v>
@@ -4890,16 +5540,16 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H155" s="1" t="b">
         <v>1</v>
@@ -4914,16 +5564,16 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H156" s="1" t="b">
         <v>1</v>
@@ -4935,22 +5585,22 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H157" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
@@ -4959,16 +5609,16 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H158" s="1" t="b">
         <v>1</v>
@@ -4983,16 +5633,16 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D159" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="H159" s="1" t="b">
         <v>1</v>
@@ -5007,16 +5657,16 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H160" s="1" t="b">
         <v>1</v>
@@ -5031,16 +5681,16 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F161" s="1" t="b">
         <v>1</v>
@@ -5052,19 +5702,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <f t="shared" si="2"/>
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G162" s="1" t="b">
         <v>1</v>
@@ -5082,16 +5732,16 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D163" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="H163" s="1" t="b">
         <v>1</v>
@@ -5106,16 +5756,16 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H164" s="1" t="b">
         <v>1</v>
@@ -5130,16 +5780,16 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H165" s="1" t="b">
         <v>1</v>
@@ -5154,16 +5804,16 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H166" s="1" t="b">
         <v>1</v>
@@ -5178,16 +5828,16 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H167" s="1" t="b">
         <v>1</v>
@@ -5202,13 +5852,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
@@ -5217,10 +5867,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
@@ -5229,10 +5879,10 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C170" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
@@ -5241,10 +5891,10 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
@@ -5253,16 +5903,16 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C172" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C172" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="D172" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I172" s="1" t="b">
         <v>1</v>
@@ -5274,37 +5924,37 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I173" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <f t="shared" si="2"/>
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G174" s="1" t="b">
         <v>1</v>
@@ -5319,16 +5969,16 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I175" s="1" t="b">
         <v>1</v>
@@ -5340,34 +5990,34 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C176" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I176" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <f t="shared" si="2"/>
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G177" s="1" t="b">
         <v>1</v>
@@ -5382,16 +6032,16 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I178" s="1" t="b">
         <v>1</v>
@@ -5403,28 +6053,28 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G180" s="1" t="b">
         <v>1</v>
@@ -5439,16 +6089,16 @@
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I181" s="1" t="b">
         <v>1</v>
@@ -5460,10 +6110,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
@@ -5472,10 +6122,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
@@ -5484,16 +6134,16 @@
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I184" s="1" t="b">
         <v>1</v>
@@ -5505,31 +6155,31 @@
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
         <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G186" s="1" t="b">
         <v>1</v>
@@ -5541,19 +6191,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <f t="shared" si="2"/>
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G187" s="1" t="b">
         <v>1</v>
@@ -5568,10 +6218,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C188" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
@@ -5580,28 +6230,28 @@
         <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G190" s="1" t="b">
         <v>1</v>
@@ -5616,10 +6266,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
@@ -5628,10 +6278,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -5640,10 +6290,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -5652,10 +6302,10 @@
         <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -5664,10 +6314,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
@@ -5676,10 +6326,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -5688,10 +6338,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
@@ -5700,10 +6350,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -5712,10 +6362,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C199" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="C199" s="5" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
@@ -5724,10 +6374,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
@@ -5736,10 +6386,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
@@ -5748,10 +6398,10 @@
         <v>201</v>
       </c>
       <c r="B202" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C202" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="C202" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
@@ -5760,10 +6410,10 @@
         <v>202</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
@@ -5772,10 +6422,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -5784,25 +6434,25 @@
         <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C205" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="C205" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <f t="shared" si="3"/>
         <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G206" s="1" t="b">
         <v>1</v>
@@ -5817,10 +6467,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
@@ -5829,10 +6479,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -5841,10 +6491,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -5853,10 +6503,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -5865,10 +6515,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -5877,10 +6527,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -5889,10 +6539,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -5901,10 +6551,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -5913,10 +6563,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -5925,10 +6575,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -5937,10 +6587,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -5949,10 +6599,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -5961,10 +6611,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -5973,10 +6623,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -5985,10 +6635,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -5997,10 +6647,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C222" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -6009,10 +6659,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -6021,10 +6671,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C224" s="5" t="s">
         <v>268</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -6033,10 +6683,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -6045,10 +6695,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -6057,10 +6707,10 @@
         <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -6069,10 +6719,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -6081,10 +6731,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -6093,10 +6743,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -6105,10 +6755,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -6117,10 +6767,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -6129,10 +6779,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -6141,10 +6791,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -6153,10 +6803,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -6165,10 +6815,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -6177,10 +6827,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -6189,10 +6839,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -6201,10 +6851,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -6213,10 +6863,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
@@ -6225,10 +6875,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
@@ -6237,10 +6887,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
@@ -6249,10 +6899,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
@@ -6261,10 +6911,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
@@ -6273,10 +6923,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C245" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
@@ -6285,28 +6935,28 @@
         <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G247" s="1" t="b">
         <v>1</v>
@@ -6315,22 +6965,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G248" s="1" t="b">
         <v>1</v>
@@ -6345,10 +6995,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C249" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
@@ -6357,10 +7007,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
@@ -6369,10 +7019,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
@@ -6381,10 +7031,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
@@ -6393,10 +7043,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C253" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
@@ -6405,16 +7055,16 @@
         <v>253</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H254" s="1" t="b">
         <v>1</v>
@@ -6429,10 +7079,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.2">
@@ -6441,10 +7091,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
@@ -6453,10 +7103,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.2">
@@ -6465,10 +7115,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
@@ -6477,10 +7127,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
@@ -6489,22 +7139,22 @@
         <v>259</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
-        <f t="shared" ref="A261:A292" si="4">A260+1</f>
+        <f t="shared" ref="A261:A293" si="4">A260+1</f>
         <v>260</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.2">
@@ -6513,10 +7163,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
@@ -6525,10 +7175,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
@@ -6537,10 +7187,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
@@ -6549,16 +7199,16 @@
         <v>264</v>
       </c>
       <c r="B265" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C265" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C265" s="5" t="s">
-        <v>135</v>
-      </c>
       <c r="D265" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H265" s="1" t="b">
         <v>1</v>
@@ -6573,16 +7223,16 @@
         <v>265</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H266" s="1" t="b">
         <v>1</v>
@@ -6597,10 +7247,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
@@ -6609,16 +7259,16 @@
         <v>267</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H268" s="1" t="b">
         <v>1</v>
@@ -6633,16 +7283,16 @@
         <v>268</v>
       </c>
       <c r="B269" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C269" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C269" s="5" t="s">
-        <v>140</v>
-      </c>
       <c r="D269" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H269" s="1" t="b">
         <v>1</v>
@@ -6657,10 +7307,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
@@ -6669,10 +7319,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
@@ -6681,10 +7331,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C272" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="C272" s="5" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.2">
@@ -6693,10 +7343,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.2">
@@ -6705,10 +7355,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.2">
@@ -6717,10 +7367,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.2">
@@ -6729,10 +7379,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.2">
@@ -6741,10 +7391,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.2">
@@ -6753,10 +7403,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.2">
@@ -6765,10 +7415,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.2">
@@ -6777,10 +7427,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.2">
@@ -6789,16 +7439,16 @@
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C281" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E281" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H281" s="1" t="b">
         <v>1</v>
@@ -6816,22 +7466,22 @@
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C282" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C282" s="5" t="s">
+      <c r="D282" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D282" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H282" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.2">
@@ -6840,22 +7490,22 @@
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H283" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.2">
@@ -6864,19 +7514,19 @@
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C284" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="E284" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.2">
@@ -6885,16 +7535,16 @@
         <v>284</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C285" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="D285" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E285" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H285" s="1" t="b">
         <v>1</v>
@@ -6909,19 +7559,19 @@
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.2">
@@ -6930,49 +7580,49 @@
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C287" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E287" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="E287" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="G287" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <f t="shared" si="4"/>
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G288" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="I288" s="1" t="b">
         <v>1</v>
@@ -6984,19 +7634,19 @@
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C289" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D289" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="E289" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
@@ -7005,22 +7655,22 @@
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
@@ -7029,38 +7679,38 @@
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <f t="shared" si="4"/>
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C292" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="E292" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D292" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E292" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="G292" s="1" t="b">
         <v>1</v>
       </c>
@@ -7069,17 +7719,21 @@
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A293" s="1">
+        <f t="shared" si="4"/>
+        <v>292</v>
+      </c>
       <c r="B293" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C293" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D293" s="1" t="s">
-        <v>397</v>
-      </c>
       <c r="E293" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H293" s="1" t="b">
         <v>1</v>
@@ -7090,18 +7744,11 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C294" s="5" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K294">
-    <filterColumn colId="6">
-      <filters blank="1">
-        <filter val="???"/>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K294"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="552">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -1683,6 +1683,15 @@
   </si>
   <si>
     <t>F_MENU_DATE_VISIT_VISITONE</t>
+  </si>
+  <si>
+    <t>F_MENU_CHEK_CHKB</t>
+  </si>
+  <si>
+    <t>F_MENU_CHEK_CHKM</t>
+  </si>
+  <si>
+    <t>WIN_CHREC_HES_BEHESABCHECK</t>
   </si>
 </sst>
 </file>
@@ -2068,6 +2077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K294"/>
   <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="22.5" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2120,7 +2130,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2146,7 +2156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -2173,7 +2183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -2200,7 +2210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2227,7 +2237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2254,7 +2264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2281,7 +2291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2308,7 +2318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2335,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2362,7 +2372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2389,7 +2399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2416,7 +2426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2443,7 +2453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2467,7 +2477,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2494,7 +2504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2521,7 +2531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2548,7 +2558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2575,7 +2585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2602,7 +2612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2626,7 +2636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2654,7 +2664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2678,7 +2688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2705,7 +2715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2732,7 +2742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2759,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2783,7 +2793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2810,7 +2820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2831,7 +2841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2843,7 +2853,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2864,7 +2874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2891,7 +2901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2921,7 +2931,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2948,7 +2958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2969,7 +2979,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2996,7 +3006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3023,7 +3033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3050,7 +3060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3077,7 +3087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3104,7 +3114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3116,7 +3126,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3143,7 +3153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3167,7 +3177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3191,7 +3201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3218,7 +3228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3245,7 +3255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3266,7 +3276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3287,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3308,7 +3318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3335,7 +3345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3359,7 +3369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3371,7 +3381,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3398,7 +3408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3425,7 +3435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3452,7 +3462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3479,7 +3489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3506,7 +3516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3530,7 +3540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3542,7 +3552,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3554,7 +3564,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3566,7 +3576,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3578,7 +3588,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3590,7 +3600,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3602,7 +3612,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3629,7 +3639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3656,7 +3666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3683,7 +3693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -3707,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <f t="shared" ref="A68:A132" si="1">A67+1</f>
         <v>67</v>
@@ -3719,7 +3729,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -3731,7 +3741,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -3758,7 +3768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -3782,7 +3792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -3794,7 +3804,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -3806,7 +3816,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -3818,7 +3828,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -3830,7 +3840,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -3842,7 +3852,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -3854,7 +3864,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -3866,7 +3876,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -3878,7 +3888,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -3890,7 +3900,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -3914,7 +3924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -3938,7 +3948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -3965,7 +3975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -3992,7 +4002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -4019,7 +4029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -4031,7 +4041,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -4055,7 +4065,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -4079,7 +4089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -4106,7 +4116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -4133,7 +4143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -4154,7 +4164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -4271,7 +4281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -4298,7 +4308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -4325,7 +4335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -4376,7 +4386,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -4403,7 +4413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4430,7 +4440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -4454,7 +4464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4478,7 +4488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4502,7 +4512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4526,7 +4536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4550,7 +4560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -4595,7 +4605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4622,7 +4632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4649,7 +4659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4676,7 +4686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4703,7 +4713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4730,7 +4740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4772,7 +4782,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -4793,7 +4803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4814,7 +4824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -4835,7 +4845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -4856,7 +4866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -4877,7 +4887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -4904,7 +4914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -4925,7 +4935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -4937,7 +4947,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -4964,7 +4974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -4985,7 +4995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -5003,7 +5013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -5024,7 +5034,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -5048,7 +5058,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -5072,7 +5082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -5099,7 +5109,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -5126,7 +5136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <f t="shared" ref="A133:A196" si="2">A132+1</f>
         <v>132</v>
@@ -5141,7 +5151,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -5168,7 +5178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -5195,7 +5205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -5207,7 +5217,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -5219,7 +5229,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -5231,7 +5241,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -5243,7 +5253,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -5255,7 +5265,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -5267,7 +5277,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -5279,7 +5289,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -5291,7 +5301,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -5303,7 +5313,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -5327,7 +5337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -5351,7 +5361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -5375,7 +5385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -5393,7 +5403,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -5417,7 +5427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -5441,7 +5451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -5465,7 +5475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -5483,7 +5493,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -5507,7 +5517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5534,7 +5544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -5558,7 +5568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -5579,7 +5589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -5603,7 +5613,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -5627,7 +5637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -5651,7 +5661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -5675,7 +5685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5702,7 +5712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5726,7 +5736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -5750,7 +5760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -5774,7 +5784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -5798,7 +5808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5822,7 +5832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -5846,7 +5856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -5861,7 +5871,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -5873,7 +5883,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -5885,7 +5895,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -5897,7 +5907,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -5918,7 +5928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -5939,7 +5949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -5963,7 +5973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -5984,7 +5994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -6005,7 +6015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -6026,7 +6036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -6047,7 +6057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -6062,7 +6072,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -6083,7 +6093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -6104,7 +6114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -6116,7 +6126,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -6128,7 +6138,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -6149,7 +6159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -6164,7 +6174,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -6191,7 +6201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -6235,8 +6245,17 @@
       <c r="C189" s="5" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D189" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="G189" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -6271,6 +6290,12 @@
       <c r="C191" s="5" t="s">
         <v>104</v>
       </c>
+      <c r="E191" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G191" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
@@ -6319,6 +6344,12 @@
       <c r="C195" s="5" t="s">
         <v>108</v>
       </c>
+      <c r="E195" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="G195" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
@@ -6331,6 +6362,9 @@
       <c r="C196" s="5" t="s">
         <v>109</v>
       </c>
+      <c r="G196" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
@@ -6416,7 +6450,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -6428,7 +6462,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -6440,7 +6474,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6461,7 +6495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -6473,7 +6507,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -6485,7 +6519,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -6497,7 +6531,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -6509,7 +6543,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -6521,7 +6555,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -6533,7 +6567,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -6545,7 +6579,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -6557,7 +6591,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -6569,7 +6603,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -6581,7 +6615,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -6593,7 +6627,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -6605,7 +6639,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -6617,7 +6651,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -6629,7 +6663,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -6641,7 +6675,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -6653,7 +6687,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -6665,7 +6699,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -6677,7 +6711,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -6689,7 +6723,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -6701,7 +6735,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6713,7 +6747,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6725,7 +6759,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6737,7 +6771,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -6749,7 +6783,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6761,7 +6795,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -6773,7 +6807,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -6785,7 +6819,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -6797,7 +6831,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -6809,7 +6843,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -6821,7 +6855,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -6833,7 +6867,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -6845,7 +6879,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6857,7 +6891,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -6869,7 +6903,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -6881,7 +6915,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -6893,7 +6927,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6905,7 +6939,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6917,7 +6951,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6929,7 +6963,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6941,7 +6975,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -6965,7 +6999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -6989,7 +7023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -7001,7 +7035,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -7013,7 +7047,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -7025,7 +7059,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -7037,7 +7071,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -7049,7 +7083,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -7073,7 +7107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -7085,7 +7119,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -7097,7 +7131,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -7109,7 +7143,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -7121,7 +7155,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -7133,7 +7167,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7145,7 +7179,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <f t="shared" ref="A261:A293" si="4">A260+1</f>
         <v>260</v>
@@ -7157,7 +7191,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <f t="shared" si="4"/>
         <v>261</v>
@@ -7169,7 +7203,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <f t="shared" si="4"/>
         <v>262</v>
@@ -7181,7 +7215,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <f t="shared" si="4"/>
         <v>263</v>
@@ -7193,7 +7227,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -7217,7 +7251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -7241,7 +7275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -7253,7 +7287,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -7277,7 +7311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -7301,7 +7335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -7313,7 +7347,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -7325,7 +7359,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -7337,7 +7371,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <f t="shared" si="4"/>
         <v>272</v>
@@ -7349,7 +7383,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <f t="shared" si="4"/>
         <v>273</v>
@@ -7361,7 +7395,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <f t="shared" si="4"/>
         <v>274</v>
@@ -7373,7 +7407,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -7385,7 +7419,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -7397,7 +7431,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -7409,7 +7443,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <f t="shared" si="4"/>
         <v>278</v>
@@ -7421,7 +7455,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -7433,7 +7467,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -7460,7 +7494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <f t="shared" si="4"/>
         <v>281</v>
@@ -7484,7 +7518,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <f t="shared" si="4"/>
         <v>282</v>
@@ -7508,7 +7542,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -7529,7 +7563,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <f t="shared" si="4"/>
         <v>284</v>
@@ -7553,7 +7587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <f t="shared" si="4"/>
         <v>285</v>
@@ -7574,7 +7608,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <f t="shared" si="4"/>
         <v>286</v>
@@ -7601,7 +7635,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -7628,7 +7662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <f t="shared" si="4"/>
         <v>288</v>
@@ -7649,7 +7683,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -7673,7 +7707,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <f t="shared" si="4"/>
         <v>290</v>
@@ -7694,7 +7728,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <f t="shared" si="4"/>
         <v>291</v>
@@ -7718,7 +7752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -7742,13 +7776,30 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="C294" s="5" t="s">
         <v>427</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K294"/>
+  <autoFilter ref="A1:K294">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="چکها - سایر گزارشات"/>
+        <filter val="چکها - سایر گزارشات - چاپ برگه به حساب گذاشتن چک"/>
+        <filter val="چکها - سایر گزارشات - چاپ چکهای پرداختی"/>
+        <filter val="خرید فروش - گزارشات خرید فروش"/>
+        <filter val="خرید فروش - گزارشات خرید فروش - گزارشات دارایی"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters blank="1">
+        <filter val="???"/>
+        <filter val="_"/>
+        <filter val="FALSE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="553">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -1692,6 +1692,9 @@
   </si>
   <si>
     <t>WIN_CHREC_HES_BEHESABCHECK</t>
+  </si>
+  <si>
+    <t>CHRE_LSPH</t>
   </si>
 </sst>
 </file>
@@ -6362,6 +6365,9 @@
       <c r="C196" s="5" t="s">
         <v>109</v>
       </c>
+      <c r="E196" s="1" t="s">
+        <v>552</v>
+      </c>
       <c r="G196" s="1" t="b">
         <v>1</v>
       </c>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -2080,19 +2080,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K294"/>
   <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="22.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="80.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.625" style="5" customWidth="1"/>
     <col min="4" max="4" width="56.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="13.75" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="21.625" style="1"/>
@@ -2133,7 +2132,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2159,7 +2158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -2186,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -2213,7 +2212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2240,7 +2239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2267,7 +2266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2294,7 +2293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2321,7 +2320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2348,7 +2347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2375,7 +2374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2402,7 +2401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2429,7 +2428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2456,7 +2455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2480,7 +2479,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2507,7 +2506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2534,7 +2533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2561,7 +2560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2588,7 +2587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2615,7 +2614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2639,7 +2638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2667,7 +2666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2691,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2718,7 +2717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2745,7 +2744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2772,7 +2771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2796,7 +2795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2823,7 +2822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2844,7 +2843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2856,7 +2855,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2877,7 +2876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2904,7 +2903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2934,7 +2933,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2961,7 +2960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2982,7 +2981,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3009,7 +3008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3036,7 +3035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3063,7 +3062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3090,7 +3089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3117,7 +3116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3129,7 +3128,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3156,7 +3155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3180,7 +3179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3204,7 +3203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3231,7 +3230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3258,7 +3257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3279,7 +3278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3300,7 +3299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3321,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3348,7 +3347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3372,7 +3371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3384,7 +3383,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3411,7 +3410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3438,7 +3437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3465,7 +3464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3492,7 +3491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3519,7 +3518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3543,7 +3542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -3555,7 +3554,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -3567,7 +3566,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -3579,7 +3578,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -3591,7 +3590,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -3603,7 +3602,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -3615,7 +3614,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3642,7 +3641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3669,7 +3668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3696,7 +3695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -3720,7 +3719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <f t="shared" ref="A68:A132" si="1">A67+1</f>
         <v>67</v>
@@ -3732,7 +3731,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -3744,7 +3743,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -3771,7 +3770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -3795,7 +3794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -3807,7 +3806,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -3819,7 +3818,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -3831,7 +3830,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -3843,7 +3842,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -3855,7 +3854,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -3867,7 +3866,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -3879,7 +3878,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -3891,7 +3890,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -3903,7 +3902,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -3927,7 +3926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -3951,7 +3950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -3978,7 +3977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -4005,7 +4004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -4032,7 +4031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -4044,7 +4043,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -4068,7 +4067,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -4092,7 +4091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -4119,7 +4118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -4146,7 +4145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -4167,7 +4166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -4284,7 +4283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -4311,7 +4310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -4338,7 +4337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -4389,7 +4388,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -4416,7 +4415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4443,7 +4442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -4467,7 +4466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4491,7 +4490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4515,7 +4514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4539,7 +4538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4563,7 +4562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -4608,7 +4607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4635,7 +4634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4662,7 +4661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4689,7 +4688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4716,7 +4715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4743,7 +4742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4785,7 +4784,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -4806,7 +4805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4827,7 +4826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -4848,7 +4847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -4869,7 +4868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -4890,7 +4889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -4917,7 +4916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -4938,7 +4937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -4950,7 +4949,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -4977,7 +4976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -4998,7 +4997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -5016,7 +5015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -5037,7 +5036,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -5061,7 +5060,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -5085,7 +5084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -5112,7 +5111,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -5139,7 +5138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <f t="shared" ref="A133:A196" si="2">A132+1</f>
         <v>132</v>
@@ -5154,7 +5153,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -5181,7 +5180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -5208,7 +5207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -5220,7 +5219,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -5232,7 +5231,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -5244,7 +5243,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -5256,7 +5255,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -5268,7 +5267,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -5280,7 +5279,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -5292,7 +5291,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -5304,7 +5303,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -5316,7 +5315,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -5340,7 +5339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -5364,7 +5363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -5388,7 +5387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -5406,7 +5405,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -5430,7 +5429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -5454,7 +5453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -5478,7 +5477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -5496,7 +5495,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -5520,7 +5519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5547,7 +5546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -5571,7 +5570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -5592,7 +5591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -5616,7 +5615,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -5640,7 +5639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -5664,7 +5663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -5688,7 +5687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5715,7 +5714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5739,7 +5738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -5763,7 +5762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -5787,7 +5786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -5811,7 +5810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -5835,7 +5834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -5859,7 +5858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -5874,7 +5873,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -5886,7 +5885,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -5898,7 +5897,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -5910,7 +5909,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -5931,7 +5930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -5952,7 +5951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -5976,7 +5975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -5997,7 +5996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -6018,7 +6017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -6039,7 +6038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -6060,7 +6059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -6075,7 +6074,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -6096,7 +6095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -6117,7 +6116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -6129,7 +6128,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -6141,7 +6140,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -6162,7 +6161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -6177,7 +6176,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -6204,7 +6203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -6258,7 +6257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -6456,7 +6455,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -6468,7 +6467,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -6480,7 +6479,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6501,7 +6500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -6513,7 +6512,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -6525,7 +6524,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -6537,7 +6536,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -6549,7 +6548,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -6561,7 +6560,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -6573,7 +6572,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -6585,7 +6584,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -6597,7 +6596,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -6609,7 +6608,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -6621,7 +6620,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -6633,7 +6632,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -6645,7 +6644,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -6657,7 +6656,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -6669,7 +6668,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -6681,7 +6680,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -6693,7 +6692,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -6705,7 +6704,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -6717,7 +6716,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -6729,7 +6728,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -6741,7 +6740,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -6753,7 +6752,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -6765,7 +6764,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -6777,7 +6776,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -6789,7 +6788,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -6801,7 +6800,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -6813,7 +6812,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -6825,7 +6824,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -6837,7 +6836,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -6849,7 +6848,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -6861,7 +6860,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -6873,7 +6872,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -6885,7 +6884,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -6897,7 +6896,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -6909,7 +6908,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" s="1">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -6921,7 +6920,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" s="1">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -6933,7 +6932,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" s="1">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -6945,7 +6944,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -6957,7 +6956,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -6969,7 +6968,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" s="1">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -6981,7 +6980,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -7005,7 +7004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -7029,7 +7028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -7041,7 +7040,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -7053,7 +7052,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -7065,7 +7064,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -7077,7 +7076,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -7089,7 +7088,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -7113,7 +7112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -7125,7 +7124,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -7137,7 +7136,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -7149,7 +7148,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -7161,7 +7160,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -7173,7 +7172,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7185,7 +7184,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <f t="shared" ref="A261:A293" si="4">A260+1</f>
         <v>260</v>
@@ -7197,7 +7196,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <f t="shared" si="4"/>
         <v>261</v>
@@ -7209,7 +7208,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" s="1">
         <f t="shared" si="4"/>
         <v>262</v>
@@ -7221,7 +7220,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
         <f t="shared" si="4"/>
         <v>263</v>
@@ -7233,7 +7232,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" s="1">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -7257,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" s="1">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -7281,7 +7280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" s="1">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -7293,7 +7292,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" s="1">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -7317,7 +7316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" s="1">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -7341,7 +7340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" s="1">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -7353,7 +7352,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" s="1">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -7365,7 +7364,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" s="1">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -7377,7 +7376,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="273" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="1">
         <f t="shared" si="4"/>
         <v>272</v>
@@ -7389,7 +7388,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="274" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="1">
         <f t="shared" si="4"/>
         <v>273</v>
@@ -7401,7 +7400,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="275" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="1">
         <f t="shared" si="4"/>
         <v>274</v>
@@ -7413,7 +7412,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="276" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="1">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -7425,7 +7424,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="277" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="1">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -7437,7 +7436,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="278" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="1">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -7449,7 +7448,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="279" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="1">
         <f t="shared" si="4"/>
         <v>278</v>
@@ -7461,7 +7460,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="280" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="1">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -7473,7 +7472,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="281" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="1">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -7500,7 +7499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="1">
         <f t="shared" si="4"/>
         <v>281</v>
@@ -7524,7 +7523,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="283" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="1">
         <f t="shared" si="4"/>
         <v>282</v>
@@ -7548,7 +7547,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="284" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="1">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -7569,7 +7568,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="285" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="1">
         <f t="shared" si="4"/>
         <v>284</v>
@@ -7593,7 +7592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="1">
         <f t="shared" si="4"/>
         <v>285</v>
@@ -7614,7 +7613,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="287" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="1">
         <f t="shared" si="4"/>
         <v>286</v>
@@ -7641,7 +7640,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -7668,7 +7667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" s="1">
         <f t="shared" si="4"/>
         <v>288</v>
@@ -7689,7 +7688,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" s="1">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -7713,7 +7712,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" s="1">
         <f t="shared" si="4"/>
         <v>290</v>
@@ -7734,7 +7733,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <f t="shared" si="4"/>
         <v>291</v>
@@ -7758,7 +7757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" s="1">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -7782,30 +7781,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C294" s="5" t="s">
         <v>427</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K294">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="چکها - سایر گزارشات"/>
-        <filter val="چکها - سایر گزارشات - چاپ برگه به حساب گذاشتن چک"/>
-        <filter val="چکها - سایر گزارشات - چاپ چکهای پرداختی"/>
-        <filter val="خرید فروش - گزارشات خرید فروش"/>
-        <filter val="خرید فروش - گزارشات خرید فروش - گزارشات دارایی"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters blank="1">
-        <filter val="???"/>
-        <filter val="_"/>
-        <filter val="FALSE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K294"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="553">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -551,9 +551,6 @@
     <t>گزارش فروش به تفکیک واحد ها</t>
   </si>
   <si>
-    <t xml:space="preserve">لیست جمع فروش کالا ها به تفکیک کالا </t>
-  </si>
-  <si>
     <t>لیست خرید به تفکیک کالا</t>
   </si>
   <si>
@@ -1695,6 +1692,9 @@
   </si>
   <si>
     <t>CHRE_LSPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لیست جمع فروش کالا ها به تفکیک (نوع) کالا </t>
   </si>
 </sst>
 </file>
@@ -2084,11 +2084,11 @@
   <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="22.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="45.625" style="5" customWidth="1"/>
     <col min="4" max="4" width="56.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.25" style="1" customWidth="1"/>
@@ -2108,28 +2108,28 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -2143,10 +2143,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -2170,10 +2170,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -2194,13 +2194,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>1</v>
@@ -2224,10 +2224,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -2248,13 +2248,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -2278,10 +2278,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -2305,10 +2305,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -2332,10 +2332,10 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G9" s="1" t="b">
         <v>1</v>
@@ -2359,10 +2359,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G10" s="1" t="b">
         <v>1</v>
@@ -2386,10 +2386,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G11" s="1" t="b">
         <v>1</v>
@@ -2413,10 +2413,10 @@
         <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G12" s="1" t="b">
         <v>1</v>
@@ -2440,10 +2440,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -2464,19 +2464,19 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>471</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -2491,10 +2491,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G15" s="1" t="b">
         <v>1</v>
@@ -2518,10 +2518,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G16" s="1" t="b">
         <v>1</v>
@@ -2545,10 +2545,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -2572,10 +2572,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -2599,10 +2599,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -2626,16 +2626,19 @@
         <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H20" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -2650,10 +2653,10 @@
         <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1" t="b">
@@ -2678,12 +2681,15 @@
         <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G22" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I22" s="1" t="b">
@@ -2702,10 +2708,10 @@
         <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G23" s="1" t="b">
         <v>1</v>
@@ -2729,10 +2735,10 @@
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -2756,10 +2762,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -2783,13 +2789,16 @@
         <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="I26" s="1" t="b">
         <v>1</v>
@@ -2807,10 +2816,10 @@
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -2834,12 +2843,18 @@
         <v>28</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2867,9 +2882,12 @@
         <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I30" s="1" t="b">
@@ -2888,10 +2906,10 @@
         <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -2915,10 +2933,10 @@
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G32" s="1" t="b">
         <v>1</v>
@@ -2930,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -2945,10 +2963,10 @@
         <v>33</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G33" s="1" t="b">
         <v>1</v>
@@ -2972,13 +2990,13 @@
         <v>34</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
@@ -2993,10 +3011,10 @@
         <v>35</v>
       </c>
       <c r="D35" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="G35" s="1" t="b">
         <v>1</v>
@@ -3020,10 +3038,10 @@
         <v>36</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -3047,10 +3065,10 @@
         <v>37</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G37" s="1" t="b">
         <v>1</v>
@@ -3074,10 +3092,10 @@
         <v>38</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G38" s="1" t="b">
         <v>1</v>
@@ -3101,10 +3119,10 @@
         <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G39" s="1" t="b">
         <v>1</v>
@@ -3127,6 +3145,15 @@
       <c r="C40" s="5" t="s">
         <v>40</v>
       </c>
+      <c r="G40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
@@ -3140,10 +3167,10 @@
         <v>41</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G41" s="1" t="b">
         <v>1</v>
@@ -3164,16 +3191,19 @@
         <v>19</v>
       </c>
       <c r="C42" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>474</v>
-      </c>
       <c r="E42" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G42" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="I42" s="1" t="b">
         <v>1</v>
@@ -3191,13 +3221,16 @@
         <v>42</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G43" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="I43" s="1" t="b">
         <v>1</v>
@@ -3215,10 +3248,10 @@
         <v>44</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G44" s="1" t="b">
         <v>1</v>
@@ -3242,10 +3275,10 @@
         <v>45</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G45" s="1" t="b">
         <v>1</v>
@@ -3269,12 +3302,18 @@
         <v>47</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H46" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3290,12 +3329,18 @@
         <v>48</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H47" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3311,12 +3356,18 @@
         <v>49</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3332,10 +3383,10 @@
         <v>50</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -3356,15 +3407,18 @@
         <v>46</v>
       </c>
       <c r="C50" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G50" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I50" s="1" t="b">
@@ -3382,6 +3436,18 @@
       <c r="C51" s="5" t="s">
         <v>51</v>
       </c>
+      <c r="F51" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="G51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
@@ -3392,13 +3458,13 @@
         <v>46</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -3422,16 +3488,19 @@
         <v>52</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G53" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="I53" s="1" t="b">
         <v>1</v>
@@ -3449,10 +3518,10 @@
         <v>53</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>459</v>
       </c>
       <c r="G54" s="1" t="b">
         <v>1</v>
@@ -3476,10 +3545,10 @@
         <v>54</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G55" s="1" t="b">
         <v>1</v>
@@ -3503,10 +3572,10 @@
         <v>55</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -3530,7 +3599,7 @@
         <v>56</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G57" s="1" t="b">
         <v>1</v>
@@ -3626,10 +3695,10 @@
         <v>66</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G64" s="1" t="b">
         <v>1</v>
@@ -3653,10 +3722,10 @@
         <v>67</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G65" s="1" t="b">
         <v>1</v>
@@ -3680,10 +3749,10 @@
         <v>68</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G66" s="1" t="b">
         <v>1</v>
@@ -3707,12 +3776,15 @@
         <v>69</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G67" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H67" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I67" s="1" t="b">
@@ -3755,10 +3827,10 @@
         <v>72</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G70" s="1" t="b">
         <v>1</v>
@@ -3782,15 +3854,18 @@
         <v>73</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G71" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H71" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I71" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3914,15 +3989,18 @@
         <v>84</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G81" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H81" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3938,15 +4016,18 @@
         <v>85</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G82" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H82" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I82" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3962,10 +4043,10 @@
         <v>152</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G83" s="1" t="b">
         <v>1</v>
@@ -3989,10 +4070,10 @@
         <v>154</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G84" s="1" t="b">
         <v>1</v>
@@ -4016,10 +4097,10 @@
         <v>155</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G85" s="1" t="b">
         <v>1</v>
@@ -4055,16 +4136,16 @@
         <v>157</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
@@ -4076,13 +4157,16 @@
         <v>153</v>
       </c>
       <c r="C88" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
+      </c>
+      <c r="G88" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H88" s="1" t="b">
         <v>1</v>
@@ -4100,13 +4184,13 @@
         <v>153</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G89" s="1" t="b">
         <v>1</v>
@@ -4127,13 +4211,13 @@
         <v>153</v>
       </c>
       <c r="C90" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G90" s="1" t="b">
         <v>1</v>
@@ -4157,12 +4241,18 @@
         <v>158</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G91" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4178,12 +4268,18 @@
         <v>159</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G92" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H92" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4199,10 +4295,13 @@
         <v>160</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
+      </c>
+      <c r="G93" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H93" s="1" t="b">
         <v>1</v>
@@ -4220,13 +4319,16 @@
         <v>161</v>
       </c>
       <c r="C94" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>384</v>
+      <c r="G94" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H94" s="1" t="b">
         <v>1</v>
@@ -4247,10 +4349,13 @@
         <v>162</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
+      </c>
+      <c r="G95" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H95" s="1" t="b">
         <v>1</v>
@@ -4271,10 +4376,13 @@
         <v>163</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
+      </c>
+      <c r="G96" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H96" s="1" t="b">
         <v>1</v>
@@ -4295,10 +4403,10 @@
         <v>164</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G97" s="1" t="b">
         <v>1</v>
@@ -4322,10 +4430,10 @@
         <v>165</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G98" s="1" t="b">
         <v>1</v>
@@ -4349,10 +4457,10 @@
         <v>166</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G99" s="1" t="b">
         <v>1</v>
@@ -4376,16 +4484,19 @@
         <v>168</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
+      </c>
+      <c r="G100" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H100" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
@@ -4400,10 +4511,10 @@
         <v>169</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G101" s="1" t="b">
         <v>1</v>
@@ -4427,10 +4538,10 @@
         <v>170</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G102" s="1" t="b">
         <v>1</v>
@@ -4451,18 +4562,21 @@
         <v>167</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>171</v>
+        <v>552</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G103" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H103" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I103" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4475,18 +4589,21 @@
         <v>167</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G104" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H104" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4499,18 +4616,21 @@
         <v>167</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G105" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I105" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4523,18 +4643,21 @@
         <v>167</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G106" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I106" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4547,15 +4670,18 @@
         <v>167</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G107" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I107" s="1" t="b">
@@ -4571,13 +4697,13 @@
         <v>167</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G108" s="1" t="b">
         <v>1</v>
@@ -4598,10 +4724,10 @@
         <v>167</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F109" s="1" t="b">
         <v>1</v>
@@ -4616,13 +4742,13 @@
         <v>167</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G110" s="1" t="b">
         <v>1</v>
@@ -4643,13 +4769,13 @@
         <v>167</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G111" s="1" t="b">
         <v>1</v>
@@ -4670,13 +4796,13 @@
         <v>167</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G112" s="1" t="b">
         <v>1</v>
@@ -4697,13 +4823,13 @@
         <v>167</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G113" s="1" t="b">
         <v>1</v>
@@ -4724,13 +4850,13 @@
         <v>167</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G114" s="1" t="b">
         <v>1</v>
@@ -4751,13 +4877,13 @@
         <v>167</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G115" s="1" t="b">
         <v>1</v>
@@ -4778,10 +4904,10 @@
         <v>167</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
@@ -4790,18 +4916,24 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G117" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H117" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I117" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4811,18 +4943,24 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C118" s="5" t="s">
-        <v>187</v>
-      </c>
       <c r="D118" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G118" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H118" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I118" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4832,18 +4970,24 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G119" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H119" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I119" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4853,18 +4997,24 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G120" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H120" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I120" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4874,18 +5024,24 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G121" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H121" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I121" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4895,16 +5051,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G122" s="1" t="b">
         <v>1</v>
@@ -4922,18 +5078,24 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C123" s="5" t="s">
-        <v>193</v>
-      </c>
       <c r="D123" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G123" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H123" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I123" s="1" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4943,10 +5105,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
@@ -4955,16 +5117,16 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G125" s="1" t="b">
         <v>1</v>
@@ -4982,16 +5144,16 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G126" s="1" t="b">
         <v>1</v>
@@ -5003,13 +5165,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F127" s="1" t="b">
         <v>1</v>
@@ -5021,19 +5183,19 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C128" s="5" t="s">
-        <v>199</v>
-      </c>
       <c r="D128" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="F128" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J128" s="1" t="s">
         <v>490</v>
-      </c>
-      <c r="F128" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
@@ -5042,22 +5204,22 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="G129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J129" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="G129" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
@@ -5066,16 +5228,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G130" s="1" t="b">
         <v>1</v>
@@ -5090,16 +5252,16 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G131" s="1" t="b">
         <v>1</v>
@@ -5108,7 +5270,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
@@ -5117,16 +5279,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G132" s="1" t="b">
         <v>1</v>
@@ -5144,13 +5306,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
@@ -5159,16 +5321,16 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G134" s="1" t="b">
         <v>1</v>
@@ -5186,16 +5348,16 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G135" s="1" t="b">
         <v>1</v>
@@ -5213,10 +5375,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
@@ -5225,10 +5387,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
@@ -5237,10 +5399,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -5249,10 +5411,10 @@
         <v>138</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
@@ -5261,10 +5423,10 @@
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
@@ -5273,10 +5435,10 @@
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
@@ -5285,10 +5447,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
@@ -5297,10 +5459,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
@@ -5309,10 +5471,10 @@
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
@@ -5321,16 +5483,16 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H145" s="1" t="b">
         <v>1</v>
@@ -5345,16 +5507,16 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C146" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C146" s="5" t="s">
-        <v>218</v>
-      </c>
       <c r="D146" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H146" s="1" t="b">
         <v>1</v>
@@ -5369,16 +5531,16 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H147" s="1" t="b">
         <v>1</v>
@@ -5393,16 +5555,16 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
@@ -5411,16 +5573,16 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H149" s="1" t="b">
         <v>1</v>
@@ -5435,16 +5597,16 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H150" s="1" t="b">
         <v>1</v>
@@ -5459,16 +5621,16 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H151" s="1" t="b">
         <v>1</v>
@@ -5483,16 +5645,16 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
@@ -5501,16 +5663,16 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H153" s="1" t="b">
         <v>1</v>
@@ -5525,16 +5687,16 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G154" s="1" t="b">
         <v>1</v>
@@ -5552,16 +5714,16 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H155" s="1" t="b">
         <v>1</v>
@@ -5576,16 +5738,16 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H156" s="1" t="b">
         <v>1</v>
@@ -5597,22 +5759,22 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H157" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
@@ -5621,16 +5783,16 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H158" s="1" t="b">
         <v>1</v>
@@ -5645,16 +5807,16 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D159" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="H159" s="1" t="b">
         <v>1</v>
@@ -5669,16 +5831,16 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H160" s="1" t="b">
         <v>1</v>
@@ -5693,16 +5855,16 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F161" s="1" t="b">
         <v>1</v>
@@ -5720,13 +5882,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G162" s="1" t="b">
         <v>1</v>
@@ -5744,16 +5906,16 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D163" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>439</v>
       </c>
       <c r="H163" s="1" t="b">
         <v>1</v>
@@ -5768,16 +5930,16 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H164" s="1" t="b">
         <v>1</v>
@@ -5792,16 +5954,16 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H165" s="1" t="b">
         <v>1</v>
@@ -5816,16 +5978,16 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H166" s="1" t="b">
         <v>1</v>
@@ -5840,16 +6002,16 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H167" s="1" t="b">
         <v>1</v>
@@ -5864,13 +6026,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
@@ -5879,10 +6041,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
@@ -5891,10 +6053,10 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C170" s="5" t="s">
         <v>242</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
@@ -5903,10 +6065,10 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
@@ -5921,10 +6083,10 @@
         <v>87</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I172" s="1" t="b">
         <v>1</v>
@@ -5942,10 +6104,10 @@
         <v>88</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I173" s="1" t="b">
         <v>1</v>
@@ -5963,10 +6125,10 @@
         <v>89</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G174" s="1" t="b">
         <v>1</v>
@@ -5987,10 +6149,10 @@
         <v>90</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I175" s="1" t="b">
         <v>1</v>
@@ -6005,13 +6167,13 @@
         <v>86</v>
       </c>
       <c r="C176" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I176" s="1" t="b">
         <v>1</v>
@@ -6026,10 +6188,10 @@
         <v>86</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G177" s="1" t="b">
         <v>1</v>
@@ -6050,10 +6212,10 @@
         <v>91</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I178" s="1" t="b">
         <v>1</v>
@@ -6071,7 +6233,7 @@
         <v>92</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
@@ -6086,7 +6248,7 @@
         <v>93</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="G180" s="1" t="b">
         <v>1</v>
@@ -6107,10 +6269,10 @@
         <v>94</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I181" s="1" t="b">
         <v>1</v>
@@ -6137,7 +6299,7 @@
         <v>86</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
@@ -6152,10 +6314,10 @@
         <v>96</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I184" s="1" t="b">
         <v>1</v>
@@ -6173,7 +6335,7 @@
         <v>97</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
@@ -6188,10 +6350,10 @@
         <v>98</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G186" s="1" t="b">
         <v>1</v>
@@ -6215,7 +6377,7 @@
         <v>99</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G187" s="1" t="b">
         <v>1</v>
@@ -6248,10 +6410,10 @@
         <v>102</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G189" s="1" t="b">
         <v>1</v>
@@ -6269,10 +6431,10 @@
         <v>103</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G190" s="1" t="b">
         <v>1</v>
@@ -6293,7 +6455,7 @@
         <v>104</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G191" s="1" t="b">
         <v>1</v>
@@ -6347,7 +6509,7 @@
         <v>108</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G195" s="1" t="b">
         <v>1</v>
@@ -6365,7 +6527,7 @@
         <v>109</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G196" s="1" t="b">
         <v>1</v>
@@ -6461,10 +6623,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -6473,10 +6635,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C205" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -6485,13 +6647,13 @@
         <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G206" s="1" t="b">
         <v>1</v>
@@ -6506,10 +6668,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
@@ -6518,10 +6680,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -6530,10 +6692,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -6542,10 +6704,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -6554,10 +6716,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -6566,10 +6728,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -6578,10 +6740,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -6590,10 +6752,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -6602,10 +6764,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -6614,10 +6776,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -6626,10 +6788,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -6638,10 +6800,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -6650,10 +6812,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -6662,10 +6824,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -6674,10 +6836,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -6686,10 +6848,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C222" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="C222" s="5" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -6698,10 +6860,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -6710,10 +6872,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C224" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -6722,10 +6884,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -6734,10 +6896,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -6746,10 +6908,10 @@
         <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -6758,10 +6920,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -6770,10 +6932,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -6782,10 +6944,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -6794,10 +6956,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -6806,10 +6968,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -6818,10 +6980,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -6830,10 +6992,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -6842,10 +7004,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -6854,10 +7016,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -6866,10 +7028,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -6878,10 +7040,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -6890,10 +7052,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -6902,10 +7064,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
@@ -6914,10 +7076,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
@@ -6926,10 +7088,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
@@ -6938,10 +7100,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
@@ -6950,10 +7112,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
@@ -6962,10 +7124,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C245" s="5" t="s">
         <v>289</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
@@ -6974,10 +7136,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
@@ -6986,16 +7148,16 @@
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G247" s="1" t="b">
         <v>1</v>
@@ -7010,16 +7172,16 @@
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G248" s="1" t="b">
         <v>1</v>
@@ -7034,10 +7196,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C249" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
@@ -7046,10 +7208,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
@@ -7058,10 +7220,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
@@ -7097,13 +7259,13 @@
         <v>121</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H254" s="1" t="b">
         <v>1</v>
@@ -7244,10 +7406,10 @@
         <v>134</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H265" s="1" t="b">
         <v>1</v>
@@ -7268,10 +7430,10 @@
         <v>135</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H266" s="1" t="b">
         <v>1</v>
@@ -7304,10 +7466,10 @@
         <v>137</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H268" s="1" t="b">
         <v>1</v>
@@ -7328,10 +7490,10 @@
         <v>139</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H269" s="1" t="b">
         <v>1</v>
@@ -7478,16 +7640,16 @@
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C281" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E281" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H281" s="1" t="b">
         <v>1</v>
@@ -7505,22 +7667,22 @@
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C282" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="C282" s="5" t="s">
+      <c r="D282" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="D282" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H282" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.2">
@@ -7529,22 +7691,22 @@
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H283" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.2">
@@ -7553,19 +7715,19 @@
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="D284" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C284" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="E284" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.2">
@@ -7577,13 +7739,13 @@
         <v>138</v>
       </c>
       <c r="C285" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D285" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E285" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H285" s="1" t="b">
         <v>1</v>
@@ -7598,19 +7760,19 @@
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.2">
@@ -7619,25 +7781,25 @@
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C287" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E287" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="E287" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="G287" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.2">
@@ -7646,22 +7808,22 @@
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G288" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="I288" s="1" t="b">
         <v>1</v>
@@ -7673,19 +7835,19 @@
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C289" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D289" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="E289" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
@@ -7694,22 +7856,22 @@
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
@@ -7718,19 +7880,19 @@
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
@@ -7739,16 +7901,16 @@
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C292" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E292" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="E292" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="G292" s="1" t="b">
         <v>1</v>
@@ -7766,13 +7928,13 @@
         <v>19</v>
       </c>
       <c r="C293" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D293" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="E293" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H293" s="1" t="b">
         <v>1</v>
@@ -7783,7 +7945,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C294" s="5" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="554">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -1695,6 +1695,9 @@
   </si>
   <si>
     <t xml:space="preserve">لیست جمع فروش کالا ها به تفکیک (نوع) کالا </t>
+  </si>
+  <si>
+    <t>VISITORS_PORSANT_HEAD</t>
   </si>
 </sst>
 </file>
@@ -5110,6 +5113,15 @@
       <c r="C124" s="5" t="s">
         <v>193</v>
       </c>
+      <c r="G124" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H124" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I124" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
@@ -5218,6 +5230,12 @@
       <c r="G129" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="H129" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I129" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="J129" s="1" t="s">
         <v>492</v>
       </c>
@@ -5245,6 +5263,9 @@
       <c r="H130" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="I130" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
@@ -5269,6 +5290,9 @@
       <c r="H131" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="I131" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="J131" s="1" t="s">
         <v>494</v>
       </c>
@@ -5379,6 +5403,18 @@
       </c>
       <c r="C136" s="5" t="s">
         <v>206</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="G136" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H136" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I136" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="559">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -662,18 +662,6 @@
     <t>تعریف اهداف برای ویزیتور ها بر اساس کالا</t>
   </si>
   <si>
-    <t>مشاهده عملکرد (اهدف) هر ویزیتور به تفکیک ماه</t>
-  </si>
-  <si>
-    <t>مشاهده عملکرد (اهدف) هر ویزیتور به تفکیک ماه (در تاریخ برگشت)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> مشاهده عملکرد (اهدف) هر ویزیتور به تفکیک ماه بر اساس گروه</t>
-  </si>
-  <si>
-    <t>مشاهده عملکرد (اهدف) هری ویزیتور به تفکیک ماه بر اساس گروه (در تاریخ برگشت)</t>
-  </si>
-  <si>
     <t>مشاهده مسیر حرکت ویزیتور روی نقشه</t>
   </si>
   <si>
@@ -1698,6 +1686,33 @@
   </si>
   <si>
     <t>VISITORS_PORSANT_HEAD</t>
+  </si>
+  <si>
+    <t>WIN_VISITGOL_HEAD_AHDAF</t>
+  </si>
+  <si>
+    <t>VISITOR_GOL_REP</t>
+  </si>
+  <si>
+    <t>مشاهده عملکرد (اهداف) هر ویزیتور به تفکیک ماه</t>
+  </si>
+  <si>
+    <t>مشاهده عملکرد (اهداف) هر ویزیتور به تفکیک ماه (در تاریخ برگشت)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> مشاهده عملکرد (اهداف) هر ویزیتور به تفکیک ماه بر اساس گروه</t>
+  </si>
+  <si>
+    <t>VISITOR_GOL_GRP_REP</t>
+  </si>
+  <si>
+    <t>VISITOR_GOL_REP_MAR</t>
+  </si>
+  <si>
+    <t>مشاهده عملکرد (اهداف) هر ویزیتور به تفکیک ماه بر اساس گروه (در تاریخ برگشت)</t>
+  </si>
+  <si>
+    <t>VISITOR_GOL_GRP_REP_MAR</t>
   </si>
 </sst>
 </file>
@@ -2088,7 +2103,7 @@
   <cols>
     <col min="1" max="1" width="10.25" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="47.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="45.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="56" style="5" customWidth="1"/>
     <col min="4" max="4" width="56.375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="41.75" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.5" style="1" customWidth="1"/>
@@ -2111,28 +2126,28 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -2146,10 +2161,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -2173,10 +2188,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -2197,13 +2212,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>1</v>
@@ -2227,10 +2242,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -2251,13 +2266,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -2281,10 +2296,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -2308,10 +2323,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -2335,10 +2350,10 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G9" s="1" t="b">
         <v>1</v>
@@ -2362,10 +2377,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G10" s="1" t="b">
         <v>1</v>
@@ -2389,10 +2404,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G11" s="1" t="b">
         <v>1</v>
@@ -2416,10 +2431,10 @@
         <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G12" s="1" t="b">
         <v>1</v>
@@ -2443,10 +2458,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -2467,19 +2482,19 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
@@ -2494,10 +2509,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G15" s="1" t="b">
         <v>1</v>
@@ -2521,10 +2536,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G16" s="1" t="b">
         <v>1</v>
@@ -2548,10 +2563,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -2575,10 +2590,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -2602,10 +2617,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -2629,10 +2644,10 @@
         <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -2641,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
@@ -2656,10 +2671,10 @@
         <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1" t="b">
@@ -2684,10 +2699,10 @@
         <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="G22" s="1" t="b">
         <v>1</v>
@@ -2711,10 +2726,10 @@
         <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G23" s="1" t="b">
         <v>1</v>
@@ -2738,10 +2753,10 @@
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -2765,10 +2780,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -2792,16 +2807,16 @@
         <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I26" s="1" t="b">
         <v>1</v>
@@ -2819,10 +2834,10 @@
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -2846,10 +2861,10 @@
         <v>28</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G28" s="1" t="b">
         <v>1</v>
@@ -2885,7 +2900,7 @@
         <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G30" s="1" t="b">
         <v>1</v>
@@ -2909,10 +2924,10 @@
         <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -2936,10 +2951,10 @@
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="G32" s="1" t="b">
         <v>1</v>
@@ -2951,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -2966,10 +2981,10 @@
         <v>33</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="G33" s="1" t="b">
         <v>1</v>
@@ -2993,13 +3008,13 @@
         <v>34</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
@@ -3014,10 +3029,10 @@
         <v>35</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="G35" s="1" t="b">
         <v>1</v>
@@ -3041,10 +3056,10 @@
         <v>36</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -3068,10 +3083,10 @@
         <v>37</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="G37" s="1" t="b">
         <v>1</v>
@@ -3095,10 +3110,10 @@
         <v>38</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="G38" s="1" t="b">
         <v>1</v>
@@ -3122,10 +3137,10 @@
         <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G39" s="1" t="b">
         <v>1</v>
@@ -3170,10 +3185,10 @@
         <v>41</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G41" s="1" t="b">
         <v>1</v>
@@ -3194,19 +3209,19 @@
         <v>19</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="G42" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I42" s="1" t="b">
         <v>1</v>
@@ -3224,16 +3239,16 @@
         <v>42</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G43" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I43" s="1" t="b">
         <v>1</v>
@@ -3251,10 +3266,10 @@
         <v>44</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G44" s="1" t="b">
         <v>1</v>
@@ -3278,10 +3293,10 @@
         <v>45</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G45" s="1" t="b">
         <v>1</v>
@@ -3305,10 +3320,10 @@
         <v>47</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G46" s="1" t="b">
         <v>1</v>
@@ -3332,10 +3347,10 @@
         <v>48</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="G47" s="1" t="b">
         <v>1</v>
@@ -3359,10 +3374,10 @@
         <v>49</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -3386,10 +3401,10 @@
         <v>50</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -3410,13 +3425,13 @@
         <v>46</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -3440,7 +3455,7 @@
         <v>51</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>0</v>
@@ -3461,13 +3476,13 @@
         <v>46</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -3491,19 +3506,19 @@
         <v>52</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G53" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I53" s="1" t="b">
         <v>1</v>
@@ -3521,10 +3536,10 @@
         <v>53</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G54" s="1" t="b">
         <v>1</v>
@@ -3548,10 +3563,10 @@
         <v>54</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="G55" s="1" t="b">
         <v>1</v>
@@ -3575,10 +3590,10 @@
         <v>55</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -3602,7 +3617,7 @@
         <v>56</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="G57" s="1" t="b">
         <v>1</v>
@@ -3698,10 +3713,10 @@
         <v>66</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="G64" s="1" t="b">
         <v>1</v>
@@ -3725,10 +3740,10 @@
         <v>67</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="G65" s="1" t="b">
         <v>1</v>
@@ -3752,10 +3767,10 @@
         <v>68</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="G66" s="1" t="b">
         <v>1</v>
@@ -3779,10 +3794,10 @@
         <v>69</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="G67" s="1" t="b">
         <v>1</v>
@@ -3830,10 +3845,10 @@
         <v>72</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="G70" s="1" t="b">
         <v>1</v>
@@ -3857,10 +3872,10 @@
         <v>73</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="G71" s="1" t="b">
         <v>1</v>
@@ -3992,10 +4007,10 @@
         <v>84</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="G81" s="1" t="b">
         <v>1</v>
@@ -4019,10 +4034,10 @@
         <v>85</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="G82" s="1" t="b">
         <v>1</v>
@@ -4046,10 +4061,10 @@
         <v>152</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G83" s="1" t="b">
         <v>1</v>
@@ -4073,10 +4088,10 @@
         <v>154</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G84" s="1" t="b">
         <v>1</v>
@@ -4100,10 +4115,10 @@
         <v>155</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G85" s="1" t="b">
         <v>1</v>
@@ -4139,16 +4154,16 @@
         <v>157</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
@@ -4160,13 +4175,13 @@
         <v>153</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G88" s="1" t="b">
         <v>1</v>
@@ -4187,13 +4202,13 @@
         <v>153</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G89" s="1" t="b">
         <v>1</v>
@@ -4214,13 +4229,13 @@
         <v>153</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G90" s="1" t="b">
         <v>1</v>
@@ -4244,10 +4259,10 @@
         <v>158</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -4271,10 +4286,10 @@
         <v>159</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G92" s="1" t="b">
         <v>1</v>
@@ -4298,10 +4313,10 @@
         <v>160</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="G93" s="1" t="b">
         <v>1</v>
@@ -4322,13 +4337,13 @@
         <v>161</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="G94" s="1" t="b">
         <v>1</v>
@@ -4352,10 +4367,10 @@
         <v>162</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G95" s="1" t="b">
         <v>1</v>
@@ -4379,10 +4394,10 @@
         <v>163</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="G96" s="1" t="b">
         <v>1</v>
@@ -4406,10 +4421,10 @@
         <v>164</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G97" s="1" t="b">
         <v>1</v>
@@ -4433,10 +4448,10 @@
         <v>165</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="G98" s="1" t="b">
         <v>1</v>
@@ -4460,10 +4475,10 @@
         <v>166</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G99" s="1" t="b">
         <v>1</v>
@@ -4487,10 +4502,10 @@
         <v>168</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G100" s="1" t="b">
         <v>1</v>
@@ -4499,7 +4514,7 @@
         <v>1</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
@@ -4514,10 +4529,10 @@
         <v>169</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="G101" s="1" t="b">
         <v>1</v>
@@ -4541,10 +4556,10 @@
         <v>170</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G102" s="1" t="b">
         <v>1</v>
@@ -4565,13 +4580,13 @@
         <v>167</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="G103" s="1" t="b">
         <v>1</v>
@@ -4595,10 +4610,10 @@
         <v>171</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="G104" s="1" t="b">
         <v>1</v>
@@ -4622,10 +4637,10 @@
         <v>172</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="G105" s="1" t="b">
         <v>1</v>
@@ -4649,10 +4664,10 @@
         <v>173</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="G106" s="1" t="b">
         <v>1</v>
@@ -4676,10 +4691,10 @@
         <v>174</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G107" s="1" t="b">
         <v>1</v>
@@ -4703,10 +4718,10 @@
         <v>175</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="G108" s="1" t="b">
         <v>1</v>
@@ -4730,7 +4745,7 @@
         <v>176</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F109" s="1" t="b">
         <v>1</v>
@@ -4748,10 +4763,10 @@
         <v>177</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="G110" s="1" t="b">
         <v>1</v>
@@ -4775,10 +4790,10 @@
         <v>178</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="G111" s="1" t="b">
         <v>1</v>
@@ -4802,10 +4817,10 @@
         <v>179</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="G112" s="1" t="b">
         <v>1</v>
@@ -4829,10 +4844,10 @@
         <v>180</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G113" s="1" t="b">
         <v>1</v>
@@ -4856,10 +4871,10 @@
         <v>181</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="G114" s="1" t="b">
         <v>1</v>
@@ -4883,10 +4898,10 @@
         <v>182</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="G115" s="1" t="b">
         <v>1</v>
@@ -4910,7 +4925,7 @@
         <v>183</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
@@ -4925,10 +4940,10 @@
         <v>184</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="G117" s="1" t="b">
         <v>1</v>
@@ -4952,10 +4967,10 @@
         <v>186</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G118" s="1" t="b">
         <v>1</v>
@@ -4979,10 +4994,10 @@
         <v>187</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G119" s="1" t="b">
         <v>1</v>
@@ -5006,10 +5021,10 @@
         <v>188</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G120" s="1" t="b">
         <v>1</v>
@@ -5033,10 +5048,10 @@
         <v>189</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G121" s="1" t="b">
         <v>1</v>
@@ -5060,10 +5075,10 @@
         <v>190</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G122" s="1" t="b">
         <v>1</v>
@@ -5087,10 +5102,10 @@
         <v>192</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="G123" s="1" t="b">
         <v>1</v>
@@ -5135,10 +5150,10 @@
         <v>194</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="G125" s="1" t="b">
         <v>1</v>
@@ -5162,10 +5177,10 @@
         <v>195</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="G126" s="1" t="b">
         <v>1</v>
@@ -5183,7 +5198,7 @@
         <v>196</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F127" s="1" t="b">
         <v>1</v>
@@ -5201,13 +5216,13 @@
         <v>198</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F128" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.2">
@@ -5222,10 +5237,10 @@
         <v>199</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="G129" s="1" t="b">
         <v>1</v>
@@ -5237,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.2">
@@ -5252,10 +5267,10 @@
         <v>200</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="G130" s="1" t="b">
         <v>1</v>
@@ -5279,10 +5294,10 @@
         <v>201</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G131" s="1" t="b">
         <v>1</v>
@@ -5294,7 +5309,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
@@ -5309,10 +5324,10 @@
         <v>202</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="G132" s="1" t="b">
         <v>1</v>
@@ -5336,7 +5351,7 @@
         <v>203</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
@@ -5351,10 +5366,10 @@
         <v>204</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G134" s="1" t="b">
         <v>1</v>
@@ -5378,10 +5393,10 @@
         <v>205</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G135" s="1" t="b">
         <v>1</v>
@@ -5405,7 +5420,7 @@
         <v>206</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="G136" s="1" t="b">
         <v>1</v>
@@ -5428,6 +5443,18 @@
       <c r="C137" s="5" t="s">
         <v>207</v>
       </c>
+      <c r="D137" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G137" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H137" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
@@ -5438,7 +5465,19 @@
         <v>197</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>208</v>
+        <v>552</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="G138" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H138" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I138" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.2">
@@ -5450,7 +5489,19 @@
         <v>197</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>209</v>
+        <v>553</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="G139" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H139" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I139" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.2">
@@ -5462,7 +5513,19 @@
         <v>197</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>210</v>
+        <v>554</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="G140" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H140" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I140" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
@@ -5474,7 +5537,19 @@
         <v>197</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>211</v>
+        <v>557</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G141" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H141" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
@@ -5486,7 +5561,7 @@
         <v>197</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
@@ -5498,7 +5573,7 @@
         <v>191</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
@@ -5510,7 +5585,7 @@
         <v>191</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
@@ -5519,16 +5594,16 @@
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="H145" s="1" t="b">
         <v>1</v>
@@ -5543,16 +5618,16 @@
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H146" s="1" t="b">
         <v>1</v>
@@ -5567,16 +5642,16 @@
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="H147" s="1" t="b">
         <v>1</v>
@@ -5591,16 +5666,16 @@
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C148" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C148" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="D148" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
@@ -5609,16 +5684,16 @@
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="H149" s="1" t="b">
         <v>1</v>
@@ -5633,16 +5708,16 @@
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="H150" s="1" t="b">
         <v>1</v>
@@ -5657,16 +5732,16 @@
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H151" s="1" t="b">
         <v>1</v>
@@ -5681,16 +5756,16 @@
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
@@ -5699,16 +5774,16 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H153" s="1" t="b">
         <v>1</v>
@@ -5723,16 +5798,16 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="G154" s="1" t="b">
         <v>1</v>
@@ -5750,16 +5825,16 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="H155" s="1" t="b">
         <v>1</v>
@@ -5774,16 +5849,16 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="H156" s="1" t="b">
         <v>1</v>
@@ -5795,22 +5870,22 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H157" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
@@ -5819,16 +5894,16 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H158" s="1" t="b">
         <v>1</v>
@@ -5843,16 +5918,16 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H159" s="1" t="b">
         <v>1</v>
@@ -5867,16 +5942,16 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="H160" s="1" t="b">
         <v>1</v>
@@ -5891,16 +5966,16 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="F161" s="1" t="b">
         <v>1</v>
@@ -5918,13 +5993,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G162" s="1" t="b">
         <v>1</v>
@@ -5942,16 +6017,16 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="H163" s="1" t="b">
         <v>1</v>
@@ -5966,16 +6041,16 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="H164" s="1" t="b">
         <v>1</v>
@@ -5990,16 +6065,16 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="H165" s="1" t="b">
         <v>1</v>
@@ -6014,16 +6089,16 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="H166" s="1" t="b">
         <v>1</v>
@@ -6038,16 +6113,16 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="H167" s="1" t="b">
         <v>1</v>
@@ -6062,13 +6137,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
@@ -6077,10 +6152,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
@@ -6089,10 +6164,10 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
@@ -6101,10 +6176,10 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
@@ -6119,10 +6194,10 @@
         <v>87</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="I172" s="1" t="b">
         <v>1</v>
@@ -6140,10 +6215,10 @@
         <v>88</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="I173" s="1" t="b">
         <v>1</v>
@@ -6161,10 +6236,10 @@
         <v>89</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G174" s="1" t="b">
         <v>1</v>
@@ -6185,10 +6260,10 @@
         <v>90</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="I175" s="1" t="b">
         <v>1</v>
@@ -6203,13 +6278,13 @@
         <v>86</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="I176" s="1" t="b">
         <v>1</v>
@@ -6224,10 +6299,10 @@
         <v>86</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="G177" s="1" t="b">
         <v>1</v>
@@ -6248,10 +6323,10 @@
         <v>91</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="I178" s="1" t="b">
         <v>1</v>
@@ -6269,7 +6344,7 @@
         <v>92</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
@@ -6284,7 +6359,7 @@
         <v>93</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="G180" s="1" t="b">
         <v>1</v>
@@ -6305,10 +6380,10 @@
         <v>94</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="I181" s="1" t="b">
         <v>1</v>
@@ -6335,7 +6410,7 @@
         <v>86</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
@@ -6350,10 +6425,10 @@
         <v>96</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="I184" s="1" t="b">
         <v>1</v>
@@ -6371,7 +6446,7 @@
         <v>97</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
@@ -6386,10 +6461,10 @@
         <v>98</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="G186" s="1" t="b">
         <v>1</v>
@@ -6413,7 +6488,7 @@
         <v>99</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="G187" s="1" t="b">
         <v>1</v>
@@ -6446,10 +6521,10 @@
         <v>102</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="G189" s="1" t="b">
         <v>1</v>
@@ -6467,10 +6542,10 @@
         <v>103</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="G190" s="1" t="b">
         <v>1</v>
@@ -6491,7 +6566,7 @@
         <v>104</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="G191" s="1" t="b">
         <v>1</v>
@@ -6545,7 +6620,7 @@
         <v>108</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="G195" s="1" t="b">
         <v>1</v>
@@ -6563,7 +6638,7 @@
         <v>109</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="G196" s="1" t="b">
         <v>1</v>
@@ -6659,10 +6734,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -6671,10 +6746,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -6683,13 +6758,13 @@
         <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="G206" s="1" t="b">
         <v>1</v>
@@ -6704,10 +6779,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
@@ -6716,10 +6791,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C208" s="5" t="s">
         <v>245</v>
-      </c>
-      <c r="C208" s="5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -6728,10 +6803,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -6740,10 +6815,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -6752,10 +6827,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -6764,10 +6839,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -6776,10 +6851,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -6788,10 +6863,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -6800,10 +6875,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -6812,10 +6887,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -6824,10 +6899,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -6836,10 +6911,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -6848,10 +6923,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -6860,10 +6935,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -6872,10 +6947,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -6884,10 +6959,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -6896,10 +6971,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -6908,10 +6983,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -6920,10 +6995,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -6932,10 +7007,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -6944,10 +7019,10 @@
         <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C227" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="C227" s="5" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -6956,10 +7031,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -6968,10 +7043,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -6980,10 +7055,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -6992,10 +7067,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -7004,10 +7079,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -7016,10 +7091,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -7028,10 +7103,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -7040,10 +7115,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -7052,10 +7127,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -7064,10 +7139,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -7076,10 +7151,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -7088,10 +7163,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -7100,10 +7175,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
@@ -7112,10 +7187,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
@@ -7124,10 +7199,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
@@ -7136,10 +7211,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
@@ -7148,10 +7223,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
@@ -7160,10 +7235,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
@@ -7172,10 +7247,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
@@ -7184,16 +7259,16 @@
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="G247" s="1" t="b">
         <v>1</v>
@@ -7208,16 +7283,16 @@
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G248" s="1" t="b">
         <v>1</v>
@@ -7232,10 +7307,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
@@ -7244,10 +7319,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
@@ -7256,10 +7331,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
@@ -7295,13 +7370,13 @@
         <v>121</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="H254" s="1" t="b">
         <v>1</v>
@@ -7442,10 +7517,10 @@
         <v>134</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H265" s="1" t="b">
         <v>1</v>
@@ -7466,10 +7541,10 @@
         <v>135</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="H266" s="1" t="b">
         <v>1</v>
@@ -7502,10 +7577,10 @@
         <v>137</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H268" s="1" t="b">
         <v>1</v>
@@ -7526,10 +7601,10 @@
         <v>139</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H269" s="1" t="b">
         <v>1</v>
@@ -7676,16 +7751,16 @@
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C281" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E281" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="E281" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="H281" s="1" t="b">
         <v>1</v>
@@ -7703,22 +7778,22 @@
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="H282" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.2">
@@ -7727,22 +7802,22 @@
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C283" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="C283" s="5" t="s">
-        <v>326</v>
-      </c>
       <c r="D283" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="H283" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.2">
@@ -7751,19 +7826,19 @@
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.2">
@@ -7775,13 +7850,13 @@
         <v>138</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="H285" s="1" t="b">
         <v>1</v>
@@ -7796,19 +7871,19 @@
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.2">
@@ -7817,25 +7892,25 @@
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G287" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.2">
@@ -7844,22 +7919,22 @@
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G288" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="I288" s="1" t="b">
         <v>1</v>
@@ -7871,19 +7946,19 @@
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
@@ -7892,22 +7967,22 @@
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
@@ -7916,19 +7991,19 @@
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
@@ -7937,16 +8012,16 @@
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G292" s="1" t="b">
         <v>1</v>
@@ -7964,13 +8039,13 @@
         <v>19</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="H293" s="1" t="b">
         <v>1</v>
@@ -7981,7 +8056,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C294" s="5" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/Doc/Mr Correct Menu.xlsx
+++ b/Doc/Mr Correct Menu.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="584">
   <si>
     <t>MS Access Menu</t>
   </si>
@@ -836,18 +836,12 @@
     <t>دریافت فاکتور آفلاین از فایل</t>
   </si>
   <si>
-    <t>سوابق فروش</t>
-  </si>
-  <si>
     <t>سوابق خرید</t>
   </si>
   <si>
     <t>سوابق برگشت فروش</t>
   </si>
   <si>
-    <t>سوابق برگشت خرید</t>
-  </si>
-  <si>
     <t>سوابق خدمات</t>
   </si>
   <si>
@@ -1713,6 +1707,87 @@
   </si>
   <si>
     <t>VISITOR_GOL_GRP_REP_MAR</t>
+  </si>
+  <si>
+    <t>WIN_LASTPRICE_CTRLF12</t>
+  </si>
+  <si>
+    <t>F_MENU_CHEK_RCHEKD</t>
+  </si>
+  <si>
+    <t>WIN_CHECK_MONP</t>
+  </si>
+  <si>
+    <t>سوابق فاکتور فروش</t>
+  </si>
+  <si>
+    <t>TR_HISTORY_FACTOR_FROOSH</t>
+  </si>
+  <si>
+    <t>TR_HISTORY_FACTOR_KHARID</t>
+  </si>
+  <si>
+    <t>TR_HISTORY_FROOSH_RETURN_NORMAL</t>
+  </si>
+  <si>
+    <t>TR_HISTORY_KHARID_RETURN_AZAD</t>
+  </si>
+  <si>
+    <t>سوابق برگشت خرید - آزاد</t>
+  </si>
+  <si>
+    <t>TR_PGET_HED</t>
+  </si>
+  <si>
+    <t>TR_HISTORY_HAVALE_ANBAR</t>
+  </si>
+  <si>
+    <t>TR_HISTORY_RASID_ANBAR</t>
+  </si>
+  <si>
+    <t>TR_DEED_HEAD</t>
+  </si>
+  <si>
+    <t>TR_HISTORY_ANBAR_ENTERGHAL</t>
+  </si>
+  <si>
+    <t>TR_HISTORY_STUF_DEF</t>
+  </si>
+  <si>
+    <t>USERS</t>
+  </si>
+  <si>
+    <t>NEWPASSWORD</t>
+  </si>
+  <si>
+    <t>WIN_SAZMAN_MOSHAKHASAT</t>
+  </si>
+  <si>
+    <t>WIN_AMVAL</t>
+  </si>
+  <si>
+    <t>WIN_About</t>
+  </si>
+  <si>
+    <t>WIN_GSCALE</t>
+  </si>
+  <si>
+    <t>PRICE_ELAMIE_FORM_ELAMIYEH_TAKHFIF</t>
+  </si>
+  <si>
+    <t>PRICE_GRP_FORM_GRUHBANDI_GHEYMATI</t>
+  </si>
+  <si>
+    <t>PRICE_ELAMIE_FORM_ELAMIYEH_GHEYMAT</t>
+  </si>
+  <si>
+    <t>NABZMOSH_KARSHENASH</t>
+  </si>
+  <si>
+    <t>NABZMOSH_MOSHTARI</t>
+  </si>
+  <si>
+    <t>F_MENU_SSM_TAKHIR_PAR</t>
   </si>
 </sst>
 </file>
@@ -2098,6 +2173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K294"/>
   <sheetFormatPr defaultColWidth="21.625" defaultRowHeight="22.5" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2126,31 +2202,31 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2161,10 +2237,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G2" s="1" t="b">
         <v>1</v>
@@ -2176,7 +2252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
@@ -2188,10 +2264,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>1</v>
@@ -2203,7 +2279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -2212,13 +2288,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>1</v>
@@ -2230,7 +2306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2242,10 +2318,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>1</v>
@@ -2257,7 +2333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2266,13 +2342,13 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>1</v>
@@ -2284,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2296,10 +2372,10 @@
         <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>1</v>
@@ -2311,7 +2387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2323,10 +2399,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>1</v>
@@ -2338,7 +2414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2350,10 +2426,10 @@
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G9" s="1" t="b">
         <v>1</v>
@@ -2365,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2377,10 +2453,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G10" s="1" t="b">
         <v>1</v>
@@ -2392,7 +2468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2404,10 +2480,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G11" s="1" t="b">
         <v>1</v>
@@ -2419,7 +2495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2431,10 +2507,10 @@
         <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G12" s="1" t="b">
         <v>1</v>
@@ -2446,7 +2522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2458,10 +2534,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -2482,22 +2558,22 @@
         <v>4</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2509,10 +2585,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G15" s="1" t="b">
         <v>1</v>
@@ -2524,7 +2600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2536,10 +2612,10 @@
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G16" s="1" t="b">
         <v>1</v>
@@ -2551,7 +2627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2563,10 +2639,10 @@
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G17" s="1" t="b">
         <v>1</v>
@@ -2578,7 +2654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2590,10 +2666,10 @@
         <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G18" s="1" t="b">
         <v>1</v>
@@ -2605,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2617,10 +2693,10 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>1</v>
@@ -2632,7 +2708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2644,10 +2720,10 @@
         <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>1</v>
@@ -2656,10 +2732,10 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2671,10 +2747,10 @@
         <v>18</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="1" t="b">
@@ -2687,7 +2763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2699,10 +2775,10 @@
         <v>22</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G22" s="1" t="b">
         <v>1</v>
@@ -2714,7 +2790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2726,10 +2802,10 @@
         <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G23" s="1" t="b">
         <v>1</v>
@@ -2741,7 +2817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2753,10 +2829,10 @@
         <v>24</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G24" s="1" t="b">
         <v>1</v>
@@ -2768,7 +2844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2780,10 +2856,10 @@
         <v>25</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G25" s="1" t="b">
         <v>1</v>
@@ -2795,7 +2871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2807,22 +2883,22 @@
         <v>26</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="G26" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I26" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2834,10 +2910,10 @@
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G27" s="1" t="b">
         <v>1</v>
@@ -2849,7 +2925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2861,10 +2937,10 @@
         <v>28</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G28" s="1" t="b">
         <v>1</v>
@@ -2888,7 +2964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2900,7 +2976,7 @@
         <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G30" s="1" t="b">
         <v>1</v>
@@ -2912,7 +2988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2924,10 +3000,10 @@
         <v>31</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G31" s="1" t="b">
         <v>1</v>
@@ -2939,7 +3015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2951,10 +3027,10 @@
         <v>32</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G32" s="1" t="b">
         <v>1</v>
@@ -2966,10 +3042,10 @@
         <v>1</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2981,10 +3057,10 @@
         <v>33</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G33" s="1" t="b">
         <v>1</v>
@@ -3008,16 +3084,16 @@
         <v>34</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3029,10 +3105,10 @@
         <v>35</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G35" s="1" t="b">
         <v>1</v>
@@ -3044,7 +3120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3056,10 +3132,10 @@
         <v>36</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G36" s="1" t="b">
         <v>1</v>
@@ -3071,7 +3147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3083,10 +3159,10 @@
         <v>37</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G37" s="1" t="b">
         <v>1</v>
@@ -3098,7 +3174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3110,10 +3186,10 @@
         <v>38</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G38" s="1" t="b">
         <v>1</v>
@@ -3125,7 +3201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3137,10 +3213,10 @@
         <v>39</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G39" s="1" t="b">
         <v>1</v>
@@ -3152,7 +3228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3173,7 +3249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3185,10 +3261,10 @@
         <v>41</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G41" s="1" t="b">
         <v>1</v>
@@ -3200,7 +3276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3209,25 +3285,25 @@
         <v>19</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G42" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I42" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3239,22 +3315,22 @@
         <v>42</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G43" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I43" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3266,10 +3342,10 @@
         <v>44</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G44" s="1" t="b">
         <v>1</v>
@@ -3281,7 +3357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3293,10 +3369,10 @@
         <v>45</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G45" s="1" t="b">
         <v>1</v>
@@ -3308,7 +3384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3320,10 +3396,10 @@
         <v>47</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G46" s="1" t="b">
         <v>1</v>
@@ -3335,7 +3411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3347,10 +3423,10 @@
         <v>48</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G47" s="1" t="b">
         <v>1</v>
@@ -3362,7 +3438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3374,10 +3450,10 @@
         <v>49</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G48" s="1" t="b">
         <v>1</v>
@@ -3389,7 +3465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3401,10 +3477,10 @@
         <v>50</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G49" s="1" t="b">
         <v>1</v>
@@ -3416,7 +3492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3425,13 +3501,13 @@
         <v>46</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G50" s="1" t="b">
         <v>1</v>
@@ -3455,7 +3531,7 @@
         <v>51</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G51" s="1" t="b">
         <v>0</v>
@@ -3467,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -3476,13 +3552,13 @@
         <v>46</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G52" s="1" t="b">
         <v>1</v>
@@ -3494,7 +3570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -3506,25 +3582,25 @@
         <v>52</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G53" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I53" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -3536,10 +3612,10 @@
         <v>53</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G54" s="1" t="b">
         <v>1</v>
@@ -3551,7 +3627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -3563,10 +3639,10 @@
         <v>54</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G55" s="1" t="b">
         <v>1</v>
@@ -3578,7 +3654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -3590,10 +3666,10 @@
         <v>55</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G56" s="1" t="b">
         <v>1</v>
@@ -3605,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -3617,7 +3693,7 @@
         <v>56</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G57" s="1" t="b">
         <v>1</v>
@@ -3701,7 +3777,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -3713,10 +3789,10 @@
         <v>66</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="G64" s="1" t="b">
         <v>1</v>
@@ -3728,7 +3804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -3740,10 +3816,10 @@
         <v>67</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G65" s="1" t="b">
         <v>1</v>
@@ -3755,7 +3831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -3767,10 +3843,10 @@
         <v>68</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G66" s="1" t="b">
         <v>1</v>
@@ -3782,7 +3858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -3794,10 +3870,10 @@
         <v>69</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="G67" s="1" t="b">
         <v>1</v>
@@ -3833,7 +3909,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -3845,10 +3921,10 @@
         <v>72</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G70" s="1" t="b">
         <v>1</v>
@@ -3860,7 +3936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -3872,10 +3948,10 @@
         <v>73</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="G71" s="1" t="b">
         <v>1</v>
@@ -3995,7 +4071,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -4007,10 +4083,10 @@
         <v>84</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G81" s="1" t="b">
         <v>1</v>
@@ -4022,7 +4098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -4034,10 +4110,10 @@
         <v>85</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G82" s="1" t="b">
         <v>1</v>
@@ -4049,7 +4125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -4061,10 +4137,10 @@
         <v>152</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="G83" s="1" t="b">
         <v>1</v>
@@ -4076,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -4088,10 +4164,10 @@
         <v>154</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G84" s="1" t="b">
         <v>1</v>
@@ -4103,7 +4179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -4115,10 +4191,10 @@
         <v>155</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G85" s="1" t="b">
         <v>1</v>
@@ -4154,19 +4230,19 @@
         <v>157</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -4175,13 +4251,13 @@
         <v>153</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G88" s="1" t="b">
         <v>1</v>
@@ -4193,7 +4269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -4202,13 +4278,13 @@
         <v>153</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G89" s="1" t="b">
         <v>1</v>
@@ -4220,7 +4296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -4229,13 +4305,13 @@
         <v>153</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G90" s="1" t="b">
         <v>1</v>
@@ -4247,7 +4323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -4259,10 +4335,10 @@
         <v>158</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G91" s="1" t="b">
         <v>1</v>
@@ -4274,7 +4350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -4286,10 +4362,10 @@
         <v>159</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G92" s="1" t="b">
         <v>1</v>
@@ -4301,7 +4377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -4313,10 +4389,10 @@
         <v>160</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G93" s="1" t="b">
         <v>1</v>
@@ -4328,7 +4404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -4337,13 +4413,13 @@
         <v>161</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G94" s="1" t="b">
         <v>1</v>
@@ -4355,7 +4431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -4367,10 +4443,10 @@
         <v>162</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G95" s="1" t="b">
         <v>1</v>
@@ -4382,7 +4458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -4394,10 +4470,10 @@
         <v>163</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G96" s="1" t="b">
         <v>1</v>
@@ -4409,7 +4485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -4421,10 +4497,10 @@
         <v>164</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G97" s="1" t="b">
         <v>1</v>
@@ -4436,7 +4512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -4448,10 +4524,10 @@
         <v>165</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G98" s="1" t="b">
         <v>1</v>
@@ -4463,7 +4539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -4475,10 +4551,10 @@
         <v>166</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G99" s="1" t="b">
         <v>1</v>
@@ -4490,7 +4566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -4502,10 +4578,10 @@
         <v>168</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G100" s="1" t="b">
         <v>1</v>
@@ -4514,10 +4590,10 @@
         <v>1</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -4529,10 +4605,10 @@
         <v>169</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G101" s="1" t="b">
         <v>1</v>
@@ -4544,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -4556,10 +4632,10 @@
         <v>170</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G102" s="1" t="b">
         <v>1</v>
@@ -4571,7 +4647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -4580,13 +4656,13 @@
         <v>167</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G103" s="1" t="b">
         <v>1</v>
@@ -4598,7 +4674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -4610,10 +4686,10 @@
         <v>171</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G104" s="1" t="b">
         <v>1</v>
@@ -4625,7 +4701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -4637,10 +4713,10 @@
         <v>172</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="G105" s="1" t="b">
         <v>1</v>
@@ -4652,7 +4728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -4664,10 +4740,10 @@
         <v>173</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="G106" s="1" t="b">
         <v>1</v>
@@ -4679,7 +4755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -4691,10 +4767,10 @@
         <v>174</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G107" s="1" t="b">
         <v>1</v>
@@ -4706,7 +4782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -4718,10 +4794,10 @@
         <v>175</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G108" s="1" t="b">
         <v>1</v>
@@ -4745,13 +4821,13 @@
         <v>176</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F109" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -4763,10 +4839,10 @@
         <v>177</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="G110" s="1" t="b">
         <v>1</v>
@@ -4778,7 +4854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -4790,10 +4866,10 @@
         <v>178</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="G111" s="1" t="b">
         <v>1</v>
@@ -4805,7 +4881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -4817,10 +4893,10 @@
         <v>179</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="G112" s="1" t="b">
         <v>1</v>
@@ -4832,7 +4908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -4844,10 +4920,10 @@
         <v>180</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G113" s="1" t="b">
         <v>1</v>
@@ -4859,7 +4935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -4871,10 +4947,10 @@
         <v>181</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G114" s="1" t="b">
         <v>1</v>
@@ -4886,7 +4962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -4898,10 +4974,10 @@
         <v>182</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="G115" s="1" t="b">
         <v>1</v>
@@ -4925,10 +5001,10 @@
         <v>183</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -4940,10 +5016,10 @@
         <v>184</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G117" s="1" t="b">
         <v>1</v>
@@ -4955,7 +5031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -4967,10 +5043,10 @@
         <v>186</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="G118" s="1" t="b">
         <v>1</v>
@@ -4982,7 +5058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -4994,10 +5070,10 @@
         <v>187</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G119" s="1" t="b">
         <v>1</v>
@@ -5009,7 +5085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -5021,10 +5097,10 @@
         <v>188</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G120" s="1" t="b">
         <v>1</v>
@@ -5036,7 +5112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -5048,10 +5124,10 @@
         <v>189</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G121" s="1" t="b">
         <v>1</v>
@@ -5063,7 +5139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -5075,10 +5151,10 @@
         <v>190</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G122" s="1" t="b">
         <v>1</v>
@@ -5090,7 +5166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -5102,10 +5178,10 @@
         <v>192</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G123" s="1" t="b">
         <v>1</v>
@@ -5117,7 +5193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -5138,7 +5214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -5150,10 +5226,10 @@
         <v>194</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G125" s="1" t="b">
         <v>1</v>
@@ -5165,7 +5241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -5177,10 +5253,10 @@
         <v>195</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G126" s="1" t="b">
         <v>1</v>
@@ -5198,7 +5274,7 @@
         <v>196</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F127" s="1" t="b">
         <v>1</v>
@@ -5216,16 +5292,16 @@
         <v>198</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F128" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -5237,10 +5313,10 @@
         <v>199</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G129" s="1" t="b">
         <v>1</v>
@@ -5252,10 +5328,10 @@
         <v>1</v>
       </c>
       <c r="J129" s="1" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -5267,10 +5343,10 @@
         <v>200</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="G130" s="1" t="b">
         <v>1</v>
@@ -5282,7 +5358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -5294,10 +5370,10 @@
         <v>201</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G131" s="1" t="b">
         <v>1</v>
@@ -5309,10 +5385,10 @@
         <v>1</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" si="1"/>
         <v>131</v>
@@ -5324,10 +5400,10 @@
         <v>202</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G132" s="1" t="b">
         <v>1</v>
@@ -5351,10 +5427,10 @@
         <v>203</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -5366,10 +5442,10 @@
         <v>204</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G134" s="1" t="b">
         <v>1</v>
@@ -5381,7 +5457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -5393,10 +5469,10 @@
         <v>205</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="G135" s="1" t="b">
         <v>1</v>
@@ -5408,7 +5484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -5420,7 +5496,7 @@
         <v>206</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G136" s="1" t="b">
         <v>1</v>
@@ -5432,7 +5508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -5444,7 +5520,7 @@
         <v>207</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G137" s="1" t="b">
         <v>1</v>
@@ -5453,10 +5529,10 @@
         <v>1</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -5465,10 +5541,10 @@
         <v>197</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G138" s="1" t="b">
         <v>1</v>
@@ -5480,7 +5556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -5489,10 +5565,10 @@
         <v>197</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G139" s="1" t="b">
         <v>1</v>
@@ -5504,7 +5580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -5513,10 +5589,10 @@
         <v>197</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G140" s="1" t="b">
         <v>1</v>
@@ -5528,7 +5604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -5537,10 +5613,10 @@
         <v>197</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G141" s="1" t="b">
         <v>1</v>
@@ -5564,7 +5640,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -5574,6 +5650,18 @@
       </c>
       <c r="C143" s="5" t="s">
         <v>209</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="G143" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H143" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I143" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
@@ -5588,7 +5676,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -5600,10 +5688,13 @@
         <v>211</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
+      </c>
+      <c r="G145" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H145" s="1" t="b">
         <v>1</v>
@@ -5612,7 +5703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -5624,10 +5715,13 @@
         <v>213</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
+      </c>
+      <c r="G146" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H146" s="1" t="b">
         <v>1</v>
@@ -5636,7 +5730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -5648,10 +5742,13 @@
         <v>214</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
+      </c>
+      <c r="G147" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H147" s="1" t="b">
         <v>1</v>
@@ -5672,13 +5769,13 @@
         <v>216</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -5687,13 +5784,16 @@
         <v>212</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
+      </c>
+      <c r="G149" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H149" s="1" t="b">
         <v>1</v>
@@ -5702,7 +5802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -5714,10 +5814,13 @@
         <v>217</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
+      </c>
+      <c r="G150" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H150" s="1" t="b">
         <v>1</v>
@@ -5726,7 +5829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -5738,10 +5841,13 @@
         <v>218</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
+      </c>
+      <c r="G151" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H151" s="1" t="b">
         <v>1</v>
@@ -5762,13 +5868,13 @@
         <v>219</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -5780,10 +5886,13 @@
         <v>220</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
+      </c>
+      <c r="G153" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H153" s="1" t="b">
         <v>1</v>
@@ -5792,7 +5901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -5804,10 +5913,10 @@
         <v>221</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G154" s="1" t="b">
         <v>1</v>
@@ -5831,10 +5940,10 @@
         <v>222</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="H155" s="1" t="b">
         <v>1</v>
@@ -5843,7 +5952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -5855,16 +5964,22 @@
         <v>223</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
+      </c>
+      <c r="G156" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H156" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I156" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -5876,19 +5991,22 @@
         <v>224</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
+      </c>
+      <c r="G157" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H157" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -5900,10 +6018,13 @@
         <v>225</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
+      </c>
+      <c r="G158" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H158" s="1" t="b">
         <v>1</v>
@@ -5912,7 +6033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -5924,10 +6045,13 @@
         <v>226</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
+      </c>
+      <c r="G159" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H159" s="1" t="b">
         <v>1</v>
@@ -5936,7 +6060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -5948,10 +6072,13 @@
         <v>227</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
+      </c>
+      <c r="G160" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H160" s="1" t="b">
         <v>1</v>
@@ -5960,7 +6087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -5972,14 +6099,17 @@
         <v>228</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F161" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="G161" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="H161" s="1" t="b">
         <v>1</v>
       </c>
@@ -5987,7 +6117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -5999,7 +6129,7 @@
         <v>229</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G162" s="1" t="b">
         <v>1</v>
@@ -6011,7 +6141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -6023,10 +6153,13 @@
         <v>230</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
+      </c>
+      <c r="G163" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H163" s="1" t="b">
         <v>1</v>
@@ -6035,7 +6168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -6047,10 +6180,13 @@
         <v>231</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
+      </c>
+      <c r="G164" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H164" s="1" t="b">
         <v>1</v>
@@ -6059,7 +6195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -6071,10 +6207,13 @@
         <v>232</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
+      </c>
+      <c r="G165" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H165" s="1" t="b">
         <v>1</v>
@@ -6083,7 +6222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -6095,10 +6234,13 @@
         <v>233</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
+      </c>
+      <c r="G166" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H166" s="1" t="b">
         <v>1</v>
@@ -6107,7 +6249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -6119,10 +6261,13 @@
         <v>234</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
+      </c>
+      <c r="G167" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H167" s="1" t="b">
         <v>1</v>
@@ -6143,7 +6288,7 @@
         <v>235</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
@@ -6182,7 +6327,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -6194,16 +6339,22 @@
         <v>87</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
+      </c>
+      <c r="G172" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H172" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="I172" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -6215,16 +6366,22 @@
         <v>88</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
+      </c>
+      <c r="G173" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H173" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="I173" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -6236,19 +6393,22 @@
         <v>89</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G174" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="H174" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="I174" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -6260,16 +6420,22 @@
         <v>90</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
+      </c>
+      <c r="G175" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H175" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="I175" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -6278,19 +6444,25 @@
         <v>86</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
+      </c>
+      <c r="G176" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H176" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="I176" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -6299,19 +6471,22 @@
         <v>86</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G177" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="H177" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="I177" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -6323,10 +6498,16 @@
         <v>91</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
+      </c>
+      <c r="G178" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H178" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="I178" s="1" t="b">
         <v>1</v>
@@ -6344,10 +6525,10 @@
         <v>92</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -6359,16 +6540,19 @@
         <v>93</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G180" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="H180" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="I180" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -6380,16 +6564,22 @@
         <v>94</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
+      </c>
+      <c r="G181" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H181" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="I181" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -6400,8 +6590,20 @@
       <c r="C182" s="5" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E182" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G182" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H182" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I182" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -6410,10 +6612,22 @@
         <v>86</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+        <v>393</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="G183" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H183" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I183" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -6425,10 +6639,16 @@
         <v>96</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
+      </c>
+      <c r="G184" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="H184" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="I184" s="1" t="b">
         <v>1</v>
@@ -6446,10 +6666,10 @@
         <v>97</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -6461,10 +6681,10 @@
         <v>98</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G186" s="1" t="b">
         <v>1</v>
@@ -6488,13 +6708,7 @@
         <v>99</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="G187" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="I187" s="1" t="b">
-        <v>1</v>
+        <v>436</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
@@ -6509,7 +6723,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -6521,16 +6735,22 @@
         <v>102</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G189" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H189" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I189" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -6542,19 +6762,22 @@
         <v>103</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G190" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="H190" s="1" t="b">
+        <v>1</v>
+      </c>
       <c r="I190" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -6566,10 +6789,16 @@
         <v>104</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G191" s="1" t="b">
         <v>1</v>
+      </c>
+      <c r="H191" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="I191" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
@@ -6584,7 +6813,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -6595,8 +6824,17 @@
       <c r="C193" s="5" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G193" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H193" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I193" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -6607,8 +6845,17 @@
       <c r="C194" s="5" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G194" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H194" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I194" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -6620,13 +6867,16 @@
         <v>108</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G195" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I195" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -6638,13 +6888,16 @@
         <v>109</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G196" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I196" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <f t="shared" ref="A197:A260" si="3">A196+1</f>
         <v>196</v>
@@ -6656,7 +6909,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <f t="shared" si="3"/>
         <v>197</v>
@@ -6668,7 +6921,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <f t="shared" si="3"/>
         <v>198</v>
@@ -6680,7 +6933,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -6692,7 +6945,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -6704,7 +6957,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -6716,7 +6969,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -6728,7 +6981,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -6740,7 +6993,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -6752,7 +7005,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -6764,7 +7017,7 @@
         <v>243</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G206" s="1" t="b">
         <v>1</v>
@@ -6773,7 +7026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -6785,7 +7038,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -6797,7 +7050,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -6809,7 +7062,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -6821,7 +7074,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -6833,7 +7086,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -6845,7 +7098,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -6857,7 +7110,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -6869,7 +7122,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -6881,7 +7134,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -6893,7 +7146,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -6905,7 +7158,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -6917,7 +7170,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -6929,7 +7182,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -6989,7 +7242,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -7001,7 +7254,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -7013,7 +7266,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -7022,10 +7275,16 @@
         <v>262</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+        <v>560</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="G227" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -7034,10 +7293,16 @@
         <v>262</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G228" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -7046,10 +7311,16 @@
         <v>262</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+        <v>267</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="G229" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -7058,10 +7329,16 @@
         <v>262</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="G230" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -7070,10 +7347,19 @@
         <v>262</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="G231" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="H231" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="I231" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="1">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -7082,10 +7368,16 @@
         <v>262</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="G232" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="1">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -7094,10 +7386,16 @@
         <v>262</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+        <v>270</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="G233" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="1">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -7106,10 +7404,16 @@
         <v>262</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="G234" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" s="1">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -7118,10 +7422,10 @@
         <v>262</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" s="1">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -7130,10 +7434,10 @@
         <v>262</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" s="1">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -7142,10 +7446,10 @@
         <v>262</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="1">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -7154,10 +7458,16 @@
         <v>262</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+        <v>275</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="G238" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="1">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -7166,10 +7476,16 @@
         <v>262</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="G239" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="1">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -7178,7 +7494,13 @@
         <v>262</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="G240" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
@@ -7190,7 +7512,7 @@
         <v>262</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
@@ -7202,7 +7524,7 @@
         <v>262</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
@@ -7214,31 +7536,43 @@
         <v>262</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="1">
         <f t="shared" si="3"/>
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="G244" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="1">
         <f t="shared" si="3"/>
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="G245" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
@@ -7247,28 +7581,28 @@
         <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C246" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="C246" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="1">
         <f t="shared" si="3"/>
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G247" s="1" t="b">
         <v>1</v>
@@ -7277,22 +7611,22 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="1">
         <f t="shared" si="3"/>
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G248" s="1" t="b">
         <v>1</v>
@@ -7301,43 +7635,61 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="1">
         <f t="shared" si="3"/>
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="G249" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="1">
         <f t="shared" si="3"/>
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C250" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C250" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E250" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="G250" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="1">
         <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G251" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="1">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -7348,8 +7700,17 @@
       <c r="C252" s="5" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D252" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G252" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="1">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -7360,8 +7721,14 @@
       <c r="C253" s="5" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E253" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G253" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="1">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -7370,13 +7737,16 @@
         <v>121</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
+      </c>
+      <c r="G254" s="1" t="b">
+        <v>1</v>
       </c>
       <c r="H254" s="1" t="b">
         <v>1</v>
@@ -7385,7 +7755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="1">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -7396,8 +7766,14 @@
       <c r="C255" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E255" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="G255" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="1">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -7408,8 +7784,14 @@
       <c r="C256" s="5" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E256" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="G256" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="1">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -7420,8 +7802,14 @@
       <c r="C257" s="5" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E257" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="G257" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="1">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -7432,8 +7820,14 @@
       <c r="C258" s="5" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E258" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="G258" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="1">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -7444,8 +7838,14 @@
       <c r="C259" s="5" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E259" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G259" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="1">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -7456,8 +7856,14 @@
       <c r="C260" s="5" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E260" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="G260" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="1">
         <f t="shared" ref="A261:A293" si="4">A260+1</f>
         <v>260</v>
@@ -7468,8 +7874,14 @@
       <c r="C261" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E261" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="G261" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="1">
         <f t="shared" si="4"/>
         <v>261</v>
@@ -7479,6 +7891,12 @@
       </c>
       <c r="C262" s="5" t="s">
         <v>130</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="G262" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
@@ -7492,6 +7910,9 @@
       <c r="C263" s="5" t="s">
         <v>131</v>
       </c>
+      <c r="F263" s="1" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" s="1">
@@ -7517,10 +7938,10 @@
         <v>134</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H265" s="1" t="b">
         <v>1</v>
@@ -7541,10 +7962,10 @@
         <v>135</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H266" s="1" t="b">
         <v>1</v>
@@ -7577,10 +7998,10 @@
         <v>137</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H268" s="1" t="b">
         <v>1</v>
@@ -7601,10 +8022,10 @@
         <v>139</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H269" s="1" t="b">
         <v>1</v>
@@ -7751,16 +8172,16 @@
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C281" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D281" s="1" t="s">
+      <c r="E281" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="E281" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="H281" s="1" t="b">
         <v>1</v>
@@ -7778,22 +8199,22 @@
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D282" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C282" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="E282" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H282" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.2">
@@ -7802,22 +8223,22 @@
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H283" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.2">
@@ -7826,19 +8247,19 @@
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C284" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="C284" s="5" t="s">
-        <v>334</v>
-      </c>
       <c r="D284" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.2">
@@ -7850,13 +8271,13 @@
         <v>138</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H285" s="1" t="b">
         <v>1</v>
@@ -7871,19 +8292,19 @@
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.2">
@@ -7892,49 +8313,49 @@
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G287" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="1">
         <f t="shared" si="4"/>
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G288" s="1" t="b">
         <v>1</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="I288" s="1" t="b">
         <v>1</v>
@@ -7946,19 +8367,19 @@
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
@@ -7967,22 +8388,22 @@
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
@@ -7991,37 +8412,37 @@
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="1">
         <f t="shared" si="4"/>
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G292" s="1" t="b">
         <v>1</v>
@@ -8039,13 +8460,13 @@
         <v>19</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="H293" s="1" t="b">
         <v>1</v>
@@ -8056,11 +8477,50 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C294" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K294"/>
+  <autoFilter ref="A1:K294">
+    <filterColumn colId="1">
+      <filters blank="1">
+        <filter val="اتوماسیون"/>
+        <filter val="انبار"/>
+        <filter val="انبار - سایر"/>
+        <filter val="برنامه ریزی"/>
+        <filter val="پذیرش و تعمیرگاه"/>
+        <filter val="تعاریف"/>
+        <filter val="تعمیر و نگهداری CMMS"/>
+        <filter val="تنظیمات برنامه"/>
+        <filter val="چکها"/>
+        <filter val="چکها - سایر گزارشات"/>
+        <filter val="چکها - سایر گزارشات - چاپ برگه به حساب گذاشتن چک"/>
+        <filter val="چکها - سایر گزارشات - چاپ چکهای پرداختی"/>
+        <filter val="حسابداری"/>
+        <filter val="حسابداری - تراز ها و مراکز هزینه"/>
+        <filter val="حسابداری - عملیات پایان سال"/>
+        <filter val="حسابداری صنعتی"/>
+        <filter val="خرید فروش"/>
+        <filter val="خرید فروش - عملیات ویزیتوری"/>
+        <filter val="خرید فروش - فاکتور"/>
+        <filter val="خرید فروش - گزارشات خرید فروش"/>
+        <filter val="خرید و فروش"/>
+        <filter val="داشبورد مدیریتی"/>
+        <filter val="سیستم - پشتیبان"/>
+        <filter val="سیستم - کاربری سیستم"/>
+        <filter val="گزارشات حسابداری"/>
+        <filter val="مدیریت فروش هوشمند"/>
+        <filter val="مدیریت مالی و بودجه"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters blank="1">
+        <filter val="???"/>
+        <filter val="_"/>
+        <filter val="FALSE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
